--- a/02table/TableS3_Non-additive_gene.xlsx
+++ b/02table/TableS3_Non-additive_gene.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11113"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C159480-60EE-904D-84DB-79818F75E0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9E915D-474F-5D42-8217-9D80960EA844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71360" yWindow="-1280" windowWidth="30240" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="75140" yWindow="-500" windowWidth="30240" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12920" uniqueCount="6464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12921" uniqueCount="6465">
   <si>
     <t>Gene</t>
   </si>
@@ -17704,9 +17704,6 @@
     <t>Positive</t>
   </si>
   <si>
-    <t>Median value of MPH in population (%)</t>
-  </si>
-  <si>
     <t>Zm00001d052843</t>
   </si>
   <si>
@@ -19412,13 +19409,43 @@
   </si>
   <si>
     <t>Table S3 Non-additive genes identified by expression data.</t>
+  </si>
+  <si>
+    <r>
+      <t>Median value of DMP in population (%)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>a</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>DMP represents deviation from mid-parent value.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -19449,6 +19476,21 @@
     <font>
       <b/>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -19508,12 +19550,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -19794,28 +19836,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A33762D7-63B9-7046-92E4-73A2911428A2}">
-  <dimension ref="A1:C6460"/>
+  <dimension ref="A1:C6462"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.83203125" customWidth="1"/>
-    <col min="2" max="2" width="34.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
+        <v>6462</v>
+      </c>
+      <c r="B1" s="6"/>
+    </row>
+    <row r="2" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>6463</v>
       </c>
-      <c r="B1" s="8"/>
-    </row>
-    <row r="2" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>5894</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>5891</v>
       </c>
     </row>
@@ -23627,7 +23669,7 @@
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A349" s="1" t="s">
-        <v>5895</v>
+        <v>5894</v>
       </c>
       <c r="B349" s="2">
         <v>-40.506886919999999</v>
@@ -25079,7 +25121,7 @@
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A481" s="1" t="s">
-        <v>5896</v>
+        <v>5895</v>
       </c>
       <c r="B481" s="2">
         <v>-34.010266299999998</v>
@@ -32240,7 +32282,7 @@
     </row>
     <row r="1132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1132" s="1" t="s">
-        <v>5897</v>
+        <v>5896</v>
       </c>
       <c r="B1132" s="2">
         <v>-18.180896180000001</v>
@@ -33714,7 +33756,7 @@
     </row>
     <row r="1266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1266" s="1" t="s">
-        <v>5898</v>
+        <v>5897</v>
       </c>
       <c r="B1266" s="2">
         <v>-16.134595820000001</v>
@@ -33923,7 +33965,7 @@
     </row>
     <row r="1285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1285" s="1" t="s">
-        <v>5899</v>
+        <v>5898</v>
       </c>
       <c r="B1285" s="2">
         <v>-15.899903009999999</v>
@@ -34341,7 +34383,7 @@
     </row>
     <row r="1323" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1323" s="1" t="s">
-        <v>5900</v>
+        <v>5899</v>
       </c>
       <c r="B1323" s="2">
         <v>-15.340410200000001</v>
@@ -35496,7 +35538,7 @@
     </row>
     <row r="1428" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1428" s="1" t="s">
-        <v>5901</v>
+        <v>5900</v>
       </c>
       <c r="B1428" s="2">
         <v>-13.94986357</v>
@@ -35969,7 +36011,7 @@
     </row>
     <row r="1471" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1471" s="1" t="s">
-        <v>5902</v>
+        <v>5901</v>
       </c>
       <c r="B1471" s="2">
         <v>-13.43163333</v>
@@ -36178,7 +36220,7 @@
     </row>
     <row r="1490" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1490" s="1" t="s">
-        <v>5903</v>
+        <v>5902</v>
       </c>
       <c r="B1490" s="2">
         <v>-13.19963276</v>
@@ -37740,7 +37782,7 @@
     </row>
     <row r="1632" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1632" s="1" t="s">
-        <v>5904</v>
+        <v>5903</v>
       </c>
       <c r="B1632" s="2">
         <v>-11.78692395</v>
@@ -38158,7 +38200,7 @@
     </row>
     <row r="1670" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1670" s="1" t="s">
-        <v>5905</v>
+        <v>5904</v>
       </c>
       <c r="B1670" s="2">
         <v>-11.47535452</v>
@@ -38180,7 +38222,7 @@
     </row>
     <row r="1672" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1672" s="1" t="s">
-        <v>5906</v>
+        <v>5905</v>
       </c>
       <c r="B1672" s="2">
         <v>-11.46456178</v>
@@ -38488,7 +38530,7 @@
     </row>
     <row r="1700" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1700" s="1" t="s">
-        <v>5907</v>
+        <v>5906</v>
       </c>
       <c r="B1700" s="2">
         <v>-11.2542887</v>
@@ -38719,7 +38761,7 @@
     </row>
     <row r="1721" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1721" s="1" t="s">
-        <v>5908</v>
+        <v>5907</v>
       </c>
       <c r="B1721" s="2">
         <v>-11.086651590000001</v>
@@ -38939,7 +38981,7 @@
     </row>
     <row r="1741" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1741" s="1" t="s">
-        <v>5909</v>
+        <v>5908</v>
       </c>
       <c r="B1741" s="2">
         <v>-10.869428449999999</v>
@@ -39951,7 +39993,7 @@
     </row>
     <row r="1833" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1833" s="1" t="s">
-        <v>5910</v>
+        <v>5909</v>
       </c>
       <c r="B1833" s="2">
         <v>-10.00922212</v>
@@ -40413,7 +40455,7 @@
     </row>
     <row r="1875" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1875" s="1" t="s">
-        <v>5911</v>
+        <v>5910</v>
       </c>
       <c r="B1875" s="2">
         <v>-9.6982496260000008</v>
@@ -40490,7 +40532,7 @@
     </row>
     <row r="1882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1882" s="1" t="s">
-        <v>5912</v>
+        <v>5911</v>
       </c>
       <c r="B1882" s="2">
         <v>-9.6669056849999997</v>
@@ -40633,7 +40675,7 @@
     </row>
     <row r="1895" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1895" s="1" t="s">
-        <v>5913</v>
+        <v>5912</v>
       </c>
       <c r="B1895" s="2">
         <v>-9.5220171800000006</v>
@@ -41062,7 +41104,7 @@
     </row>
     <row r="1934" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1934" s="1" t="s">
-        <v>5914</v>
+        <v>5913</v>
       </c>
       <c r="B1934" s="2">
         <v>-9.2726988039999991</v>
@@ -41161,7 +41203,7 @@
     </row>
     <row r="1943" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1943" s="1" t="s">
-        <v>5915</v>
+        <v>5914</v>
       </c>
       <c r="B1943" s="2">
         <v>-9.1958211930000004</v>
@@ -41359,7 +41401,7 @@
     </row>
     <row r="1961" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1961" s="1" t="s">
-        <v>5916</v>
+        <v>5915</v>
       </c>
       <c r="B1961" s="2">
         <v>-9.079644321</v>
@@ -41986,7 +42028,7 @@
     </row>
     <row r="2018" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2018" s="1" t="s">
-        <v>5917</v>
+        <v>5916</v>
       </c>
       <c r="B2018" s="2">
         <v>-8.595160688</v>
@@ -42195,7 +42237,7 @@
     </row>
     <row r="2037" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2037" s="1" t="s">
-        <v>5918</v>
+        <v>5917</v>
       </c>
       <c r="B2037" s="2">
         <v>-8.4390302990000006</v>
@@ -42261,7 +42303,7 @@
     </row>
     <row r="2043" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2043" s="1" t="s">
-        <v>5919</v>
+        <v>5918</v>
       </c>
       <c r="B2043" s="2">
         <v>-8.3521038349999994</v>
@@ -42767,7 +42809,7 @@
     </row>
     <row r="2089" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2089" s="1" t="s">
-        <v>5920</v>
+        <v>5919</v>
       </c>
       <c r="B2089" s="2">
         <v>-7.958479648</v>
@@ -42965,7 +43007,7 @@
     </row>
     <row r="2107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2107" s="1" t="s">
-        <v>5921</v>
+        <v>5920</v>
       </c>
       <c r="B2107" s="2">
         <v>-7.7942170810000002</v>
@@ -43218,7 +43260,7 @@
     </row>
     <row r="2130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2130" s="1" t="s">
-        <v>5922</v>
+        <v>5921</v>
       </c>
       <c r="B2130" s="2">
         <v>-7.566715437</v>
@@ -43339,7 +43381,7 @@
     </row>
     <row r="2141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2141" s="1" t="s">
-        <v>5923</v>
+        <v>5922</v>
       </c>
       <c r="B2141" s="2">
         <v>-7.4446396129999997</v>
@@ -43372,7 +43414,7 @@
     </row>
     <row r="2144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2144" s="1" t="s">
-        <v>5924</v>
+        <v>5923</v>
       </c>
       <c r="B2144" s="2">
         <v>-7.4110630280000001</v>
@@ -43427,7 +43469,7 @@
     </row>
     <row r="2149" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2149" s="1" t="s">
-        <v>5925</v>
+        <v>5924</v>
       </c>
       <c r="B2149" s="2">
         <v>-7.3708700479999996</v>
@@ -43526,7 +43568,7 @@
     </row>
     <row r="2158" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2158" s="1" t="s">
-        <v>5926</v>
+        <v>5925</v>
       </c>
       <c r="B2158" s="2">
         <v>-7.3169753679999996</v>
@@ -43625,7 +43667,7 @@
     </row>
     <row r="2167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2167" s="1" t="s">
-        <v>5927</v>
+        <v>5926</v>
       </c>
       <c r="B2167" s="2">
         <v>-7.2319148179999999</v>
@@ -43812,7 +43854,7 @@
     </row>
     <row r="2184" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2184" s="1" t="s">
-        <v>5928</v>
+        <v>5927</v>
       </c>
       <c r="B2184" s="2">
         <v>-7.1346271569999997</v>
@@ -43900,7 +43942,7 @@
     </row>
     <row r="2192" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2192" s="1" t="s">
-        <v>5929</v>
+        <v>5928</v>
       </c>
       <c r="B2192" s="2">
         <v>-7.0781661659999999</v>
@@ -44032,7 +44074,7 @@
     </row>
     <row r="2204" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2204" s="1" t="s">
-        <v>5930</v>
+        <v>5929</v>
       </c>
       <c r="B2204" s="2">
         <v>-7.0297533919999999</v>
@@ -44230,7 +44272,7 @@
     </row>
     <row r="2222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2222" s="1" t="s">
-        <v>5931</v>
+        <v>5930</v>
       </c>
       <c r="B2222" s="2">
         <v>-6.9196434</v>
@@ -44274,7 +44316,7 @@
     </row>
     <row r="2226" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2226" s="1" t="s">
-        <v>5932</v>
+        <v>5931</v>
       </c>
       <c r="B2226" s="2">
         <v>-6.8907247309999997</v>
@@ -44362,7 +44404,7 @@
     </row>
     <row r="2234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2234" s="1" t="s">
-        <v>5933</v>
+        <v>5932</v>
       </c>
       <c r="B2234" s="2">
         <v>-6.8256755670000002</v>
@@ -44417,7 +44459,7 @@
     </row>
     <row r="2239" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2239" s="1" t="s">
-        <v>5934</v>
+        <v>5933</v>
       </c>
       <c r="B2239" s="2">
         <v>-6.7708236199999998</v>
@@ -44593,7 +44635,7 @@
     </row>
     <row r="2255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2255" s="1" t="s">
-        <v>5935</v>
+        <v>5934</v>
       </c>
       <c r="B2255" s="2">
         <v>-6.6200106060000001</v>
@@ -44758,7 +44800,7 @@
     </row>
     <row r="2270" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2270" s="1" t="s">
-        <v>5936</v>
+        <v>5935</v>
       </c>
       <c r="B2270" s="2">
         <v>-6.4700815680000003</v>
@@ -44780,7 +44822,7 @@
     </row>
     <row r="2272" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2272" s="1" t="s">
-        <v>5937</v>
+        <v>5936</v>
       </c>
       <c r="B2272" s="2">
         <v>-6.4662549690000004</v>
@@ -44802,7 +44844,7 @@
     </row>
     <row r="2274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2274" s="1" t="s">
-        <v>5938</v>
+        <v>5937</v>
       </c>
       <c r="B2274" s="2">
         <v>-6.4196942029999997</v>
@@ -44813,7 +44855,7 @@
     </row>
     <row r="2275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2275" s="1" t="s">
-        <v>5939</v>
+        <v>5938</v>
       </c>
       <c r="B2275" s="2">
         <v>-6.404309638</v>
@@ -44912,7 +44954,7 @@
     </row>
     <row r="2284" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2284" s="1" t="s">
-        <v>5940</v>
+        <v>5939</v>
       </c>
       <c r="B2284" s="2">
         <v>-6.3451798239999997</v>
@@ -45330,7 +45372,7 @@
     </row>
     <row r="2322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2322" s="1" t="s">
-        <v>5941</v>
+        <v>5940</v>
       </c>
       <c r="B2322" s="2">
         <v>-6.1553045370000001</v>
@@ -45341,7 +45383,7 @@
     </row>
     <row r="2323" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2323" s="1" t="s">
-        <v>5942</v>
+        <v>5941</v>
       </c>
       <c r="B2323" s="2">
         <v>-6.1505785399999997</v>
@@ -45583,7 +45625,7 @@
     </row>
     <row r="2345" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2345" s="1" t="s">
-        <v>5943</v>
+        <v>5942</v>
       </c>
       <c r="B2345" s="2">
         <v>-6.0322396510000003</v>
@@ -45627,7 +45669,7 @@
     </row>
     <row r="2349" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2349" s="1" t="s">
-        <v>5944</v>
+        <v>5943</v>
       </c>
       <c r="B2349" s="2">
         <v>-6.0057119339999998</v>
@@ -45704,7 +45746,7 @@
     </row>
     <row r="2356" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2356" s="1" t="s">
-        <v>5945</v>
+        <v>5944</v>
       </c>
       <c r="B2356" s="2">
         <v>-5.960374335</v>
@@ -45748,7 +45790,7 @@
     </row>
     <row r="2360" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2360" s="1" t="s">
-        <v>5946</v>
+        <v>5945</v>
       </c>
       <c r="B2360" s="2">
         <v>-5.9362134390000003</v>
@@ -45759,7 +45801,7 @@
     </row>
     <row r="2361" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2361" s="1" t="s">
-        <v>5947</v>
+        <v>5946</v>
       </c>
       <c r="B2361" s="2">
         <v>-5.932880183</v>
@@ -45990,7 +46032,7 @@
     </row>
     <row r="2382" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2382" s="1" t="s">
-        <v>5948</v>
+        <v>5947</v>
       </c>
       <c r="B2382" s="2">
         <v>-5.7581214789999997</v>
@@ -46078,7 +46120,7 @@
     </row>
     <row r="2390" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2390" s="1" t="s">
-        <v>5949</v>
+        <v>5948</v>
       </c>
       <c r="B2390" s="2">
         <v>-5.6596577249999998</v>
@@ -46144,7 +46186,7 @@
     </row>
     <row r="2396" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2396" s="1" t="s">
-        <v>5950</v>
+        <v>5949</v>
       </c>
       <c r="B2396" s="2">
         <v>-5.6355119419999999</v>
@@ -46265,7 +46307,7 @@
     </row>
     <row r="2407" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2407" s="1" t="s">
-        <v>5951</v>
+        <v>5950</v>
       </c>
       <c r="B2407" s="2">
         <v>-5.5688256630000001</v>
@@ -46353,7 +46395,7 @@
     </row>
     <row r="2415" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2415" s="1" t="s">
-        <v>5952</v>
+        <v>5951</v>
       </c>
       <c r="B2415" s="2">
         <v>-5.5041244569999996</v>
@@ -46430,7 +46472,7 @@
     </row>
     <row r="2422" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2422" s="1" t="s">
-        <v>5953</v>
+        <v>5952</v>
       </c>
       <c r="B2422" s="2">
         <v>-5.4541809170000004</v>
@@ -46485,7 +46527,7 @@
     </row>
     <row r="2427" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2427" s="1" t="s">
-        <v>5954</v>
+        <v>5953</v>
       </c>
       <c r="B2427" s="2">
         <v>-5.4204470929999999</v>
@@ -46507,7 +46549,7 @@
     </row>
     <row r="2429" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2429" s="1" t="s">
-        <v>5955</v>
+        <v>5954</v>
       </c>
       <c r="B2429" s="2">
         <v>-5.4128194030000003</v>
@@ -46991,7 +47033,7 @@
     </row>
     <row r="2473" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2473" s="1" t="s">
-        <v>5956</v>
+        <v>5955</v>
       </c>
       <c r="B2473" s="2">
         <v>-5.1074625420000004</v>
@@ -47002,7 +47044,7 @@
     </row>
     <row r="2474" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2474" s="1" t="s">
-        <v>5957</v>
+        <v>5956</v>
       </c>
       <c r="B2474" s="2">
         <v>-5.0937557839999998</v>
@@ -47057,7 +47099,7 @@
     </row>
     <row r="2479" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2479" s="1" t="s">
-        <v>5958</v>
+        <v>5957</v>
       </c>
       <c r="B2479" s="2">
         <v>-5.0553409540000001</v>
@@ -47167,7 +47209,7 @@
     </row>
     <row r="2489" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2489" s="1" t="s">
-        <v>5959</v>
+        <v>5958</v>
       </c>
       <c r="B2489" s="2">
         <v>-4.9903231960000003</v>
@@ -47288,7 +47330,7 @@
     </row>
     <row r="2500" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2500" s="1" t="s">
-        <v>5960</v>
+        <v>5959</v>
       </c>
       <c r="B2500" s="2">
         <v>-4.924811139</v>
@@ -47398,7 +47440,7 @@
     </row>
     <row r="2510" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2510" s="1" t="s">
-        <v>5961</v>
+        <v>5960</v>
       </c>
       <c r="B2510" s="2">
         <v>-4.8490511459999999</v>
@@ -47420,7 +47462,7 @@
     </row>
     <row r="2512" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2512" s="1" t="s">
-        <v>5962</v>
+        <v>5961</v>
       </c>
       <c r="B2512" s="2">
         <v>-4.8300380049999996</v>
@@ -47497,7 +47539,7 @@
     </row>
     <row r="2519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2519" s="1" t="s">
-        <v>5963</v>
+        <v>5962</v>
       </c>
       <c r="B2519" s="2">
         <v>-4.8013698079999996</v>
@@ -47574,7 +47616,7 @@
     </row>
     <row r="2526" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2526" s="1" t="s">
-        <v>5964</v>
+        <v>5963</v>
       </c>
       <c r="B2526" s="2">
         <v>-4.7520028380000001</v>
@@ -47728,7 +47770,7 @@
     </row>
     <row r="2540" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2540" s="1" t="s">
-        <v>5965</v>
+        <v>5964</v>
       </c>
       <c r="B2540" s="2">
         <v>-4.6821222310000001</v>
@@ -47904,7 +47946,7 @@
     </row>
     <row r="2556" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2556" s="1" t="s">
-        <v>5966</v>
+        <v>5965</v>
       </c>
       <c r="B2556" s="2">
         <v>-4.5912140700000004</v>
@@ -48036,7 +48078,7 @@
     </row>
     <row r="2568" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2568" s="1" t="s">
-        <v>5967</v>
+        <v>5966</v>
       </c>
       <c r="B2568" s="2">
         <v>-4.5108501060000004</v>
@@ -48091,7 +48133,7 @@
     </row>
     <row r="2573" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2573" s="1" t="s">
-        <v>5968</v>
+        <v>5967</v>
       </c>
       <c r="B2573" s="2">
         <v>-4.4792332999999998</v>
@@ -48102,7 +48144,7 @@
     </row>
     <row r="2574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2574" s="1" t="s">
-        <v>5969</v>
+        <v>5968</v>
       </c>
       <c r="B2574" s="2">
         <v>-4.4765553410000001</v>
@@ -48135,7 +48177,7 @@
     </row>
     <row r="2577" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2577" s="1" t="s">
-        <v>5970</v>
+        <v>5969</v>
       </c>
       <c r="B2577" s="2">
         <v>-4.4674825089999999</v>
@@ -48201,7 +48243,7 @@
     </row>
     <row r="2583" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2583" s="1" t="s">
-        <v>5971</v>
+        <v>5970</v>
       </c>
       <c r="B2583" s="2">
         <v>-4.4411874170000001</v>
@@ -48322,7 +48364,7 @@
     </row>
     <row r="2594" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2594" s="1" t="s">
-        <v>5972</v>
+        <v>5971</v>
       </c>
       <c r="B2594" s="2">
         <v>-4.364338032</v>
@@ -48421,7 +48463,7 @@
     </row>
     <row r="2603" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2603" s="1" t="s">
-        <v>5973</v>
+        <v>5972</v>
       </c>
       <c r="B2603" s="2">
         <v>-4.3201759519999996</v>
@@ -48619,7 +48661,7 @@
     </row>
     <row r="2621" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2621" s="1" t="s">
-        <v>5974</v>
+        <v>5973</v>
       </c>
       <c r="B2621" s="2">
         <v>-4.2347917270000002</v>
@@ -48718,7 +48760,7 @@
     </row>
     <row r="2630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2630" s="1" t="s">
-        <v>5975</v>
+        <v>5974</v>
       </c>
       <c r="B2630" s="2">
         <v>-4.1967956620000004</v>
@@ -48828,7 +48870,7 @@
     </row>
     <row r="2640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2640" s="1" t="s">
-        <v>5976</v>
+        <v>5975</v>
       </c>
       <c r="B2640" s="2">
         <v>-4.1250821609999999</v>
@@ -49147,7 +49189,7 @@
     </row>
     <row r="2669" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2669" s="1" t="s">
-        <v>5977</v>
+        <v>5976</v>
       </c>
       <c r="B2669" s="2">
         <v>-3.9036391359999998</v>
@@ -49191,7 +49233,7 @@
     </row>
     <row r="2673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2673" s="1" t="s">
-        <v>5978</v>
+        <v>5977</v>
       </c>
       <c r="B2673" s="2">
         <v>-3.876513197</v>
@@ -49235,7 +49277,7 @@
     </row>
     <row r="2677" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2677" s="1" t="s">
-        <v>5979</v>
+        <v>5978</v>
       </c>
       <c r="B2677" s="2">
         <v>-3.8644723430000001</v>
@@ -49290,7 +49332,7 @@
     </row>
     <row r="2682" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2682" s="1" t="s">
-        <v>5980</v>
+        <v>5979</v>
       </c>
       <c r="B2682" s="2">
         <v>-3.804151031</v>
@@ -49345,7 +49387,7 @@
     </row>
     <row r="2687" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2687" s="1" t="s">
-        <v>5981</v>
+        <v>5980</v>
       </c>
       <c r="B2687" s="2">
         <v>-3.7839198930000002</v>
@@ -49389,7 +49431,7 @@
     </row>
     <row r="2691" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2691" s="1" t="s">
-        <v>5982</v>
+        <v>5981</v>
       </c>
       <c r="B2691" s="2">
         <v>-3.7629874089999999</v>
@@ -49411,7 +49453,7 @@
     </row>
     <row r="2693" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2693" s="1" t="s">
-        <v>5983</v>
+        <v>5982</v>
       </c>
       <c r="B2693" s="2">
         <v>-3.7572035700000002</v>
@@ -49587,7 +49629,7 @@
     </row>
     <row r="2709" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2709" s="1" t="s">
-        <v>5984</v>
+        <v>5983</v>
       </c>
       <c r="B2709" s="2">
         <v>-3.5921279209999999</v>
@@ -49631,7 +49673,7 @@
     </row>
     <row r="2713" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2713" s="1" t="s">
-        <v>5985</v>
+        <v>5984</v>
       </c>
       <c r="B2713" s="2">
         <v>-3.5825984929999999</v>
@@ -49752,7 +49794,7 @@
     </row>
     <row r="2724" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2724" s="1" t="s">
-        <v>5986</v>
+        <v>5985</v>
       </c>
       <c r="B2724" s="2">
         <v>-3.5418989359999999</v>
@@ -49928,7 +49970,7 @@
     </row>
     <row r="2740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2740" s="1" t="s">
-        <v>5987</v>
+        <v>5986</v>
       </c>
       <c r="B2740" s="2">
         <v>-3.4232389369999998</v>
@@ -49950,7 +49992,7 @@
     </row>
     <row r="2742" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2742" s="1" t="s">
-        <v>5988</v>
+        <v>5987</v>
       </c>
       <c r="B2742" s="2">
         <v>-3.4083595729999998</v>
@@ -49961,7 +50003,7 @@
     </row>
     <row r="2743" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2743" s="1" t="s">
-        <v>5989</v>
+        <v>5988</v>
       </c>
       <c r="B2743" s="2">
         <v>-3.3976883089999999</v>
@@ -50203,7 +50245,7 @@
     </row>
     <row r="2765" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2765" s="1" t="s">
-        <v>5990</v>
+        <v>5989</v>
       </c>
       <c r="B2765" s="2">
         <v>-3.2350251129999998</v>
@@ -50390,7 +50432,7 @@
     </row>
     <row r="2782" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2782" s="1" t="s">
-        <v>5991</v>
+        <v>5990</v>
       </c>
       <c r="B2782" s="2">
         <v>-3.1455244929999999</v>
@@ -50401,7 +50443,7 @@
     </row>
     <row r="2783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2783" s="1" t="s">
-        <v>5992</v>
+        <v>5991</v>
       </c>
       <c r="B2783" s="2">
         <v>-3.1439250950000002</v>
@@ -50544,7 +50586,7 @@
     </row>
     <row r="2796" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2796" s="1" t="s">
-        <v>5993</v>
+        <v>5992</v>
       </c>
       <c r="B2796" s="2">
         <v>-3.0532036159999998</v>
@@ -50841,7 +50883,7 @@
     </row>
     <row r="2823" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2823" s="1" t="s">
-        <v>5994</v>
+        <v>5993</v>
       </c>
       <c r="B2823" s="2">
         <v>-2.8744552329999999</v>
@@ -50896,7 +50938,7 @@
     </row>
     <row r="2828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2828" s="1" t="s">
-        <v>5995</v>
+        <v>5994</v>
       </c>
       <c r="B2828" s="2">
         <v>-2.8383109910000002</v>
@@ -50940,7 +50982,7 @@
     </row>
     <row r="2832" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2832" s="1" t="s">
-        <v>5996</v>
+        <v>5995</v>
       </c>
       <c r="B2832" s="2">
         <v>-2.8212542059999999</v>
@@ -50984,7 +51026,7 @@
     </row>
     <row r="2836" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2836" s="1" t="s">
-        <v>5997</v>
+        <v>5996</v>
       </c>
       <c r="B2836" s="2">
         <v>-2.79656298</v>
@@ -50995,7 +51037,7 @@
     </row>
     <row r="2837" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2837" s="1" t="s">
-        <v>5998</v>
+        <v>5997</v>
       </c>
       <c r="B2837" s="2">
         <v>-2.788674329</v>
@@ -51006,7 +51048,7 @@
     </row>
     <row r="2838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2838" s="1" t="s">
-        <v>5999</v>
+        <v>5998</v>
       </c>
       <c r="B2838" s="2">
         <v>-2.7816331079999999</v>
@@ -51116,7 +51158,7 @@
     </row>
     <row r="2848" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2848" s="1" t="s">
-        <v>6000</v>
+        <v>5999</v>
       </c>
       <c r="B2848" s="2">
         <v>-2.710153955</v>
@@ -51193,7 +51235,7 @@
     </row>
     <row r="2855" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2855" s="1" t="s">
-        <v>6001</v>
+        <v>6000</v>
       </c>
       <c r="B2855" s="2">
         <v>-2.676234107</v>
@@ -51215,7 +51257,7 @@
     </row>
     <row r="2857" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2857" s="1" t="s">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="B2857" s="2">
         <v>-2.6710954259999999</v>
@@ -51314,7 +51356,7 @@
     </row>
     <row r="2866" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2866" s="1" t="s">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="B2866" s="2">
         <v>-2.5945894940000001</v>
@@ -51545,7 +51587,7 @@
     </row>
     <row r="2887" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2887" s="1" t="s">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="B2887" s="2">
         <v>-2.4754847180000001</v>
@@ -51556,7 +51598,7 @@
     </row>
     <row r="2888" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2888" s="1" t="s">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="B2888" s="2">
         <v>-2.4690696870000002</v>
@@ -51644,7 +51686,7 @@
     </row>
     <row r="2896" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2896" s="1" t="s">
-        <v>6006</v>
+        <v>6005</v>
       </c>
       <c r="B2896" s="2">
         <v>-2.4290178870000001</v>
@@ -51666,7 +51708,7 @@
     </row>
     <row r="2898" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2898" s="1" t="s">
-        <v>6007</v>
+        <v>6006</v>
       </c>
       <c r="B2898" s="2">
         <v>-2.426946225</v>
@@ -51787,7 +51829,7 @@
     </row>
     <row r="2909" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2909" s="1" t="s">
-        <v>6008</v>
+        <v>6007</v>
       </c>
       <c r="B2909" s="2">
         <v>-2.3471523489999999</v>
@@ -51952,7 +51994,7 @@
     </row>
     <row r="2924" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2924" s="1" t="s">
-        <v>6009</v>
+        <v>6008</v>
       </c>
       <c r="B2924" s="2">
         <v>-2.2566814179999999</v>
@@ -52018,7 +52060,7 @@
     </row>
     <row r="2930" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2930" s="1" t="s">
-        <v>6010</v>
+        <v>6009</v>
       </c>
       <c r="B2930" s="2">
         <v>-2.2292156009999999</v>
@@ -52040,7 +52082,7 @@
     </row>
     <row r="2932" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2932" s="1" t="s">
-        <v>6011</v>
+        <v>6010</v>
       </c>
       <c r="B2932" s="2">
         <v>-2.2175028210000001</v>
@@ -52161,7 +52203,7 @@
     </row>
     <row r="2943" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2943" s="1" t="s">
-        <v>6012</v>
+        <v>6011</v>
       </c>
       <c r="B2943" s="2">
         <v>-2.1494690099999998</v>
@@ -52293,7 +52335,7 @@
     </row>
     <row r="2955" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2955" s="1" t="s">
-        <v>6013</v>
+        <v>6012</v>
       </c>
       <c r="B2955" s="2">
         <v>-2.067280845</v>
@@ -52337,7 +52379,7 @@
     </row>
     <row r="2959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2959" s="1" t="s">
-        <v>6014</v>
+        <v>6013</v>
       </c>
       <c r="B2959" s="2">
         <v>-2.0393698470000001</v>
@@ -52447,7 +52489,7 @@
     </row>
     <row r="2969" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2969" s="1" t="s">
-        <v>6015</v>
+        <v>6014</v>
       </c>
       <c r="B2969" s="2">
         <v>-1.9729021790000001</v>
@@ -52502,7 +52544,7 @@
     </row>
     <row r="2974" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2974" s="1" t="s">
-        <v>6016</v>
+        <v>6015</v>
       </c>
       <c r="B2974" s="2">
         <v>-1.945011265</v>
@@ -52645,7 +52687,7 @@
     </row>
     <row r="2987" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2987" s="1" t="s">
-        <v>6017</v>
+        <v>6016</v>
       </c>
       <c r="B2987" s="2">
         <v>-1.886893382</v>
@@ -52799,7 +52841,7 @@
     </row>
     <row r="3001" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3001" s="1" t="s">
-        <v>6018</v>
+        <v>6017</v>
       </c>
       <c r="B3001" s="2">
         <v>-1.8365829419999999</v>
@@ -52854,7 +52896,7 @@
     </row>
     <row r="3006" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3006" s="1" t="s">
-        <v>6019</v>
+        <v>6018</v>
       </c>
       <c r="B3006" s="2">
         <v>-1.815070011</v>
@@ -52964,7 +53006,7 @@
     </row>
     <row r="3016" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3016" s="1" t="s">
-        <v>6020</v>
+        <v>6019</v>
       </c>
       <c r="B3016" s="2">
         <v>-1.7623599210000001</v>
@@ -53019,7 +53061,7 @@
     </row>
     <row r="3021" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3021" s="1" t="s">
-        <v>6021</v>
+        <v>6020</v>
       </c>
       <c r="B3021" s="2">
         <v>-1.749757555</v>
@@ -53063,7 +53105,7 @@
     </row>
     <row r="3025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3025" s="1" t="s">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="B3025" s="2">
         <v>-1.7387023370000001</v>
@@ -53085,7 +53127,7 @@
     </row>
     <row r="3027" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3027" s="1" t="s">
-        <v>6023</v>
+        <v>6022</v>
       </c>
       <c r="B3027" s="2">
         <v>-1.7311041009999999</v>
@@ -53096,7 +53138,7 @@
     </row>
     <row r="3028" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3028" s="1" t="s">
-        <v>6024</v>
+        <v>6023</v>
       </c>
       <c r="B3028" s="2">
         <v>-1.7275018310000001</v>
@@ -53140,7 +53182,7 @@
     </row>
     <row r="3032" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3032" s="1" t="s">
-        <v>6025</v>
+        <v>6024</v>
       </c>
       <c r="B3032" s="2">
         <v>-1.702841957</v>
@@ -53261,7 +53303,7 @@
     </row>
     <row r="3043" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3043" s="1" t="s">
-        <v>6026</v>
+        <v>6025</v>
       </c>
       <c r="B3043" s="2">
         <v>-1.6771327949999999</v>
@@ -53371,7 +53413,7 @@
     </row>
     <row r="3053" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3053" s="1" t="s">
-        <v>6027</v>
+        <v>6026</v>
       </c>
       <c r="B3053" s="2">
         <v>-1.636330654</v>
@@ -53404,7 +53446,7 @@
     </row>
     <row r="3056" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3056" s="1" t="s">
-        <v>6028</v>
+        <v>6027</v>
       </c>
       <c r="B3056" s="2">
         <v>-1.6155637650000001</v>
@@ -53437,7 +53479,7 @@
     </row>
     <row r="3059" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3059" s="1" t="s">
-        <v>6029</v>
+        <v>6028</v>
       </c>
       <c r="B3059" s="2">
         <v>-1.5860285860000001</v>
@@ -53558,7 +53600,7 @@
     </row>
     <row r="3070" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3070" s="1" t="s">
-        <v>6030</v>
+        <v>6029</v>
       </c>
       <c r="B3070" s="2">
         <v>-1.5316967290000001</v>
@@ -53580,7 +53622,7 @@
     </row>
     <row r="3072" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3072" s="1" t="s">
-        <v>6031</v>
+        <v>6030</v>
       </c>
       <c r="B3072" s="2">
         <v>-1.52876546</v>
@@ -53591,7 +53633,7 @@
     </row>
     <row r="3073" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3073" s="1" t="s">
-        <v>6032</v>
+        <v>6031</v>
       </c>
       <c r="B3073" s="2">
         <v>-1.522495205</v>
@@ -53668,7 +53710,7 @@
     </row>
     <row r="3080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3080" s="1" t="s">
-        <v>6033</v>
+        <v>6032</v>
       </c>
       <c r="B3080" s="2">
         <v>-1.481087587</v>
@@ -53789,7 +53831,7 @@
     </row>
     <row r="3091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3091" s="1" t="s">
-        <v>6034</v>
+        <v>6033</v>
       </c>
       <c r="B3091" s="2">
         <v>-1.4347690470000001</v>
@@ -53910,7 +53952,7 @@
     </row>
     <row r="3102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3102" s="1" t="s">
-        <v>6035</v>
+        <v>6034</v>
       </c>
       <c r="B3102" s="2">
         <v>-1.3796192060000001</v>
@@ -53954,7 +53996,7 @@
     </row>
     <row r="3106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3106" s="1" t="s">
-        <v>6036</v>
+        <v>6035</v>
       </c>
       <c r="B3106" s="2">
         <v>-1.3728051029999999</v>
@@ -53987,7 +54029,7 @@
     </row>
     <row r="3109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3109" s="1" t="s">
-        <v>6037</v>
+        <v>6036</v>
       </c>
       <c r="B3109" s="2">
         <v>-1.3678625849999999</v>
@@ -54031,7 +54073,7 @@
     </row>
     <row r="3113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3113" s="1" t="s">
-        <v>6038</v>
+        <v>6037</v>
       </c>
       <c r="B3113" s="2">
         <v>-1.3349272160000001</v>
@@ -54053,7 +54095,7 @@
     </row>
     <row r="3115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3115" s="1" t="s">
-        <v>6039</v>
+        <v>6038</v>
       </c>
       <c r="B3115" s="2">
         <v>-1.3251150039999999</v>
@@ -54097,7 +54139,7 @@
     </row>
     <row r="3119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3119" s="1" t="s">
-        <v>6040</v>
+        <v>6039</v>
       </c>
       <c r="B3119" s="2">
         <v>-1.308453922</v>
@@ -54152,7 +54194,7 @@
     </row>
     <row r="3124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3124" s="1" t="s">
-        <v>6041</v>
+        <v>6040</v>
       </c>
       <c r="B3124" s="2">
         <v>-1.2676003680000001</v>
@@ -54218,7 +54260,7 @@
     </row>
     <row r="3130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3130" s="1" t="s">
-        <v>6042</v>
+        <v>6041</v>
       </c>
       <c r="B3130" s="2">
         <v>-1.2115584939999999</v>
@@ -54295,7 +54337,7 @@
     </row>
     <row r="3137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3137" s="1" t="s">
-        <v>6043</v>
+        <v>6042</v>
       </c>
       <c r="B3137" s="2">
         <v>-1.1928434370000001</v>
@@ -54350,7 +54392,7 @@
     </row>
     <row r="3142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3142" s="1" t="s">
-        <v>6044</v>
+        <v>6043</v>
       </c>
       <c r="B3142" s="2">
         <v>-1.1726616860000001</v>
@@ -54383,7 +54425,7 @@
     </row>
     <row r="3145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3145" s="1" t="s">
-        <v>6045</v>
+        <v>6044</v>
       </c>
       <c r="B3145" s="2">
         <v>-1.147074033</v>
@@ -54427,7 +54469,7 @@
     </row>
     <row r="3149" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3149" s="1" t="s">
-        <v>6046</v>
+        <v>6045</v>
       </c>
       <c r="B3149" s="2">
         <v>-1.131096721</v>
@@ -54449,7 +54491,7 @@
     </row>
     <row r="3151" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3151" s="1" t="s">
-        <v>6047</v>
+        <v>6046</v>
       </c>
       <c r="B3151" s="2">
         <v>-1.111413167</v>
@@ -54471,7 +54513,7 @@
     </row>
     <row r="3153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3153" s="1" t="s">
-        <v>6048</v>
+        <v>6047</v>
       </c>
       <c r="B3153" s="2">
         <v>-1.099434427</v>
@@ -54482,7 +54524,7 @@
     </row>
     <row r="3154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3154" s="1" t="s">
-        <v>6049</v>
+        <v>6048</v>
       </c>
       <c r="B3154" s="2">
         <v>-1.0986858799999999</v>
@@ -54559,7 +54601,7 @@
     </row>
     <row r="3161" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3161" s="1" t="s">
-        <v>6050</v>
+        <v>6049</v>
       </c>
       <c r="B3161" s="2">
         <v>-1.043059953</v>
@@ -54658,7 +54700,7 @@
     </row>
     <row r="3170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3170" s="1" t="s">
-        <v>6051</v>
+        <v>6050</v>
       </c>
       <c r="B3170" s="2">
         <v>-0.97919154799999997</v>
@@ -54801,7 +54843,7 @@
     </row>
     <row r="3183" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3183" s="1" t="s">
-        <v>6052</v>
+        <v>6051</v>
       </c>
       <c r="B3183" s="2">
         <v>-0.90349979499999999</v>
@@ -54955,7 +54997,7 @@
     </row>
     <row r="3197" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3197" s="1" t="s">
-        <v>6053</v>
+        <v>6052</v>
       </c>
       <c r="B3197" s="2">
         <v>-0.77869999499999998</v>
@@ -54977,7 +55019,7 @@
     </row>
     <row r="3199" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3199" s="1" t="s">
-        <v>6054</v>
+        <v>6053</v>
       </c>
       <c r="B3199" s="2">
         <v>-0.76372168200000001</v>
@@ -55021,7 +55063,7 @@
     </row>
     <row r="3203" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3203" s="1" t="s">
-        <v>6055</v>
+        <v>6054</v>
       </c>
       <c r="B3203" s="2">
         <v>-0.73027776700000002</v>
@@ -55043,7 +55085,7 @@
     </row>
     <row r="3205" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3205" s="1" t="s">
-        <v>6056</v>
+        <v>6055</v>
       </c>
       <c r="B3205" s="2">
         <v>-0.719799725</v>
@@ -55054,7 +55096,7 @@
     </row>
     <row r="3206" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3206" s="1" t="s">
-        <v>6057</v>
+        <v>6056</v>
       </c>
       <c r="B3206" s="2">
         <v>-0.70973040399999998</v>
@@ -55164,7 +55206,7 @@
     </row>
     <row r="3216" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3216" s="1" t="s">
-        <v>6058</v>
+        <v>6057</v>
       </c>
       <c r="B3216" s="2">
         <v>-0.59435600399999999</v>
@@ -55197,7 +55239,7 @@
     </row>
     <row r="3219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3219" s="1" t="s">
-        <v>6059</v>
+        <v>6058</v>
       </c>
       <c r="B3219" s="2">
         <v>-0.58187562299999995</v>
@@ -55230,7 +55272,7 @@
     </row>
     <row r="3222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3222" s="1" t="s">
-        <v>6060</v>
+        <v>6059</v>
       </c>
       <c r="B3222" s="2">
         <v>-0.56578664400000001</v>
@@ -55263,7 +55305,7 @@
     </row>
     <row r="3225" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3225" s="1" t="s">
-        <v>6061</v>
+        <v>6060</v>
       </c>
       <c r="B3225" s="2">
         <v>-0.55182751799999996</v>
@@ -55318,7 +55360,7 @@
     </row>
     <row r="3230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3230" s="1" t="s">
-        <v>6062</v>
+        <v>6061</v>
       </c>
       <c r="B3230" s="2">
         <v>-0.50530929400000002</v>
@@ -55340,7 +55382,7 @@
     </row>
     <row r="3232" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3232" s="1" t="s">
-        <v>6063</v>
+        <v>6062</v>
       </c>
       <c r="B3232" s="2">
         <v>-0.49672133899999998</v>
@@ -55428,7 +55470,7 @@
     </row>
     <row r="3240" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3240" s="1" t="s">
-        <v>6064</v>
+        <v>6063</v>
       </c>
       <c r="B3240" s="2">
         <v>-0.44962882100000001</v>
@@ -55681,7 +55723,7 @@
     </row>
     <row r="3263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3263" s="1" t="s">
-        <v>6065</v>
+        <v>6064</v>
       </c>
       <c r="B3263" s="2">
         <v>-0.32924283300000001</v>
@@ -55703,7 +55745,7 @@
     </row>
     <row r="3265" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3265" s="1" t="s">
-        <v>6066</v>
+        <v>6065</v>
       </c>
       <c r="B3265" s="2">
         <v>-0.322967014</v>
@@ -55747,7 +55789,7 @@
     </row>
     <row r="3269" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3269" s="1" t="s">
-        <v>6067</v>
+        <v>6066</v>
       </c>
       <c r="B3269" s="2">
         <v>-0.29159769000000002</v>
@@ -55813,7 +55855,7 @@
     </row>
     <row r="3275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3275" s="1" t="s">
-        <v>6068</v>
+        <v>6067</v>
       </c>
       <c r="B3275" s="2">
         <v>-0.26015781999999998</v>
@@ -55824,7 +55866,7 @@
     </row>
     <row r="3276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3276" s="1" t="s">
-        <v>6069</v>
+        <v>6068</v>
       </c>
       <c r="B3276" s="2">
         <v>-0.25331172800000001</v>
@@ -55857,7 +55899,7 @@
     </row>
     <row r="3279" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3279" s="1" t="s">
-        <v>6070</v>
+        <v>6069</v>
       </c>
       <c r="B3279" s="2">
         <v>-0.23528738499999999</v>
@@ -55890,7 +55932,7 @@
     </row>
     <row r="3282" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3282" s="1" t="s">
-        <v>6071</v>
+        <v>6070</v>
       </c>
       <c r="B3282" s="2">
         <v>-0.20621102899999999</v>
@@ -55901,7 +55943,7 @@
     </row>
     <row r="3283" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3283" s="1" t="s">
-        <v>6072</v>
+        <v>6071</v>
       </c>
       <c r="B3283" s="2">
         <v>-0.204879109</v>
@@ -56022,7 +56064,7 @@
     </row>
     <row r="3294" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3294" s="1" t="s">
-        <v>6073</v>
+        <v>6072</v>
       </c>
       <c r="B3294" s="2">
         <v>-0.12034842499999999</v>
@@ -56044,7 +56086,7 @@
     </row>
     <row r="3296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3296" s="1" t="s">
-        <v>6074</v>
+        <v>6073</v>
       </c>
       <c r="B3296" s="2">
         <v>-0.115059601</v>
@@ -56055,7 +56097,7 @@
     </row>
     <row r="3297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3297" s="1" t="s">
-        <v>6075</v>
+        <v>6074</v>
       </c>
       <c r="B3297" s="2">
         <v>-0.11155124800000001</v>
@@ -56077,7 +56119,7 @@
     </row>
     <row r="3299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3299" s="1" t="s">
-        <v>6076</v>
+        <v>6075</v>
       </c>
       <c r="B3299" s="2">
         <v>-0.10212466000000001</v>
@@ -56198,7 +56240,7 @@
     </row>
     <row r="3310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3310" s="1" t="s">
-        <v>6077</v>
+        <v>6076</v>
       </c>
       <c r="B3310" s="2">
         <v>-1.4173653E-2</v>
@@ -56220,7 +56262,7 @@
     </row>
     <row r="3312" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3312" s="1" t="s">
-        <v>6078</v>
+        <v>6077</v>
       </c>
       <c r="B3312" s="2">
         <v>-8.8892680000000005E-3</v>
@@ -56418,7 +56460,7 @@
     </row>
     <row r="3330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3330" s="1" t="s">
-        <v>6079</v>
+        <v>6078</v>
       </c>
       <c r="B3330" s="2">
         <v>5.9322379000000001E-2</v>
@@ -56539,7 +56581,7 @@
     </row>
     <row r="3341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3341" s="1" t="s">
-        <v>6080</v>
+        <v>6079</v>
       </c>
       <c r="B3341" s="2">
         <v>0.122656709</v>
@@ -56594,7 +56636,7 @@
     </row>
     <row r="3346" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3346" s="1" t="s">
-        <v>6081</v>
+        <v>6080</v>
       </c>
       <c r="B3346" s="2">
         <v>0.146238588</v>
@@ -56605,7 +56647,7 @@
     </row>
     <row r="3347" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3347" s="1" t="s">
-        <v>6082</v>
+        <v>6081</v>
       </c>
       <c r="B3347" s="2">
         <v>0.154528836</v>
@@ -56616,7 +56658,7 @@
     </row>
     <row r="3348" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3348" s="1" t="s">
-        <v>6083</v>
+        <v>6082</v>
       </c>
       <c r="B3348" s="2">
         <v>0.15836067200000001</v>
@@ -56627,7 +56669,7 @@
     </row>
     <row r="3349" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3349" s="1" t="s">
-        <v>6084</v>
+        <v>6083</v>
       </c>
       <c r="B3349" s="2">
         <v>0.17885874700000001</v>
@@ -56726,7 +56768,7 @@
     </row>
     <row r="3358" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3358" s="1" t="s">
-        <v>6085</v>
+        <v>6084</v>
       </c>
       <c r="B3358" s="2">
         <v>0.24562843000000001</v>
@@ -56748,7 +56790,7 @@
     </row>
     <row r="3360" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3360" s="1" t="s">
-        <v>6086</v>
+        <v>6085</v>
       </c>
       <c r="B3360" s="2">
         <v>0.26722009200000002</v>
@@ -56847,7 +56889,7 @@
     </row>
     <row r="3369" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3369" s="1" t="s">
-        <v>6087</v>
+        <v>6086</v>
       </c>
       <c r="B3369" s="2">
         <v>0.30538488400000002</v>
@@ -56869,7 +56911,7 @@
     </row>
     <row r="3371" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3371" s="1" t="s">
-        <v>6088</v>
+        <v>6087</v>
       </c>
       <c r="B3371" s="2">
         <v>0.317939099</v>
@@ -56880,7 +56922,7 @@
     </row>
     <row r="3372" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3372" s="1" t="s">
-        <v>6089</v>
+        <v>6088</v>
       </c>
       <c r="B3372" s="2">
         <v>0.31867003999999999</v>
@@ -56913,7 +56955,7 @@
     </row>
     <row r="3375" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3375" s="1" t="s">
-        <v>6090</v>
+        <v>6089</v>
       </c>
       <c r="B3375" s="2">
         <v>0.347147229</v>
@@ -56924,7 +56966,7 @@
     </row>
     <row r="3376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3376" s="1" t="s">
-        <v>6091</v>
+        <v>6090</v>
       </c>
       <c r="B3376" s="2">
         <v>0.36167529199999998</v>
@@ -57001,7 +57043,7 @@
     </row>
     <row r="3383" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3383" s="1" t="s">
-        <v>6092</v>
+        <v>6091</v>
       </c>
       <c r="B3383" s="2">
         <v>0.43290655900000002</v>
@@ -57089,7 +57131,7 @@
     </row>
     <row r="3391" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3391" s="1" t="s">
-        <v>6093</v>
+        <v>6092</v>
       </c>
       <c r="B3391" s="2">
         <v>0.48327849899999997</v>
@@ -57111,7 +57153,7 @@
     </row>
     <row r="3393" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3393" s="1" t="s">
-        <v>6094</v>
+        <v>6093</v>
       </c>
       <c r="B3393" s="2">
         <v>0.49876762099999999</v>
@@ -57122,7 +57164,7 @@
     </row>
     <row r="3394" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3394" s="1" t="s">
-        <v>6095</v>
+        <v>6094</v>
       </c>
       <c r="B3394" s="2">
         <v>0.50264985900000003</v>
@@ -57232,7 +57274,7 @@
     </row>
     <row r="3404" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3404" s="1" t="s">
-        <v>6096</v>
+        <v>6095</v>
       </c>
       <c r="B3404" s="2">
         <v>0.55720607200000005</v>
@@ -57254,7 +57296,7 @@
     </row>
     <row r="3406" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3406" s="1" t="s">
-        <v>6097</v>
+        <v>6096</v>
       </c>
       <c r="B3406" s="2">
         <v>0.58838143399999998</v>
@@ -57276,7 +57318,7 @@
     </row>
     <row r="3408" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3408" s="1" t="s">
-        <v>6098</v>
+        <v>6097</v>
       </c>
       <c r="B3408" s="2">
         <v>0.59664045399999999</v>
@@ -57298,7 +57340,7 @@
     </row>
     <row r="3410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3410" s="1" t="s">
-        <v>6099</v>
+        <v>6098</v>
       </c>
       <c r="B3410" s="2">
         <v>0.60655304600000004</v>
@@ -57375,7 +57417,7 @@
     </row>
     <row r="3417" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3417" s="1" t="s">
-        <v>6100</v>
+        <v>6099</v>
       </c>
       <c r="B3417" s="2">
         <v>0.64482944399999997</v>
@@ -57474,7 +57516,7 @@
     </row>
     <row r="3426" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3426" s="1" t="s">
-        <v>6101</v>
+        <v>6100</v>
       </c>
       <c r="B3426" s="2">
         <v>0.68677098800000003</v>
@@ -57507,7 +57549,7 @@
     </row>
     <row r="3429" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3429" s="1" t="s">
-        <v>6102</v>
+        <v>6101</v>
       </c>
       <c r="B3429" s="2">
         <v>0.69750383599999999</v>
@@ -57562,7 +57604,7 @@
     </row>
     <row r="3434" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3434" s="1" t="s">
-        <v>6103</v>
+        <v>6102</v>
       </c>
       <c r="B3434" s="2">
         <v>0.73261253000000004</v>
@@ -57584,7 +57626,7 @@
     </row>
     <row r="3436" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3436" s="1" t="s">
-        <v>6104</v>
+        <v>6103</v>
       </c>
       <c r="B3436" s="2">
         <v>0.74207574099999996</v>
@@ -57672,7 +57714,7 @@
     </row>
     <row r="3444" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3444" s="1" t="s">
-        <v>6105</v>
+        <v>6104</v>
       </c>
       <c r="B3444" s="2">
         <v>0.82747985700000004</v>
@@ -57683,7 +57725,7 @@
     </row>
     <row r="3445" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3445" s="1" t="s">
-        <v>6106</v>
+        <v>6105</v>
       </c>
       <c r="B3445" s="2">
         <v>0.83060382399999999</v>
@@ -57793,7 +57835,7 @@
     </row>
     <row r="3455" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3455" s="1" t="s">
-        <v>6107</v>
+        <v>6106</v>
       </c>
       <c r="B3455" s="2">
         <v>0.90355322500000002</v>
@@ -57991,7 +58033,7 @@
     </row>
     <row r="3473" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3473" s="1" t="s">
-        <v>6108</v>
+        <v>6107</v>
       </c>
       <c r="B3473" s="2">
         <v>1.022037079</v>
@@ -58057,7 +58099,7 @@
     </row>
     <row r="3479" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3479" s="1" t="s">
-        <v>6109</v>
+        <v>6108</v>
       </c>
       <c r="B3479" s="2">
         <v>1.045830316</v>
@@ -58090,7 +58132,7 @@
     </row>
     <row r="3482" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3482" s="1" t="s">
-        <v>6110</v>
+        <v>6109</v>
       </c>
       <c r="B3482" s="2">
         <v>1.0542312190000001</v>
@@ -58112,7 +58154,7 @@
     </row>
     <row r="3484" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3484" s="1" t="s">
-        <v>6111</v>
+        <v>6110</v>
       </c>
       <c r="B3484" s="2">
         <v>1.0610110989999999</v>
@@ -58233,7 +58275,7 @@
     </row>
     <row r="3495" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3495" s="1" t="s">
-        <v>6112</v>
+        <v>6111</v>
       </c>
       <c r="B3495" s="2">
         <v>1.123569051</v>
@@ -58277,7 +58319,7 @@
     </row>
     <row r="3499" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3499" s="1" t="s">
-        <v>6113</v>
+        <v>6112</v>
       </c>
       <c r="B3499" s="2">
         <v>1.140960752</v>
@@ -58288,7 +58330,7 @@
     </row>
     <row r="3500" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3500" s="1" t="s">
-        <v>6114</v>
+        <v>6113</v>
       </c>
       <c r="B3500" s="2">
         <v>1.1416899730000001</v>
@@ -58299,7 +58341,7 @@
     </row>
     <row r="3501" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3501" s="1" t="s">
-        <v>6115</v>
+        <v>6114</v>
       </c>
       <c r="B3501" s="2">
         <v>1.1449017939999999</v>
@@ -58321,7 +58363,7 @@
     </row>
     <row r="3503" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3503" s="1" t="s">
-        <v>6116</v>
+        <v>6115</v>
       </c>
       <c r="B3503" s="2">
         <v>1.149980835</v>
@@ -58354,7 +58396,7 @@
     </row>
     <row r="3506" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3506" s="1" t="s">
-        <v>6117</v>
+        <v>6116</v>
       </c>
       <c r="B3506" s="2">
         <v>1.154893403</v>
@@ -58376,7 +58418,7 @@
     </row>
     <row r="3508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3508" s="1" t="s">
-        <v>6118</v>
+        <v>6117</v>
       </c>
       <c r="B3508" s="2">
         <v>1.186467827</v>
@@ -58442,7 +58484,7 @@
     </row>
     <row r="3514" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3514" s="1" t="s">
-        <v>6119</v>
+        <v>6118</v>
       </c>
       <c r="B3514" s="2">
         <v>1.214450085</v>
@@ -58563,7 +58605,7 @@
     </row>
     <row r="3525" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3525" s="1" t="s">
-        <v>6120</v>
+        <v>6119</v>
       </c>
       <c r="B3525" s="2">
         <v>1.2809979389999999</v>
@@ -58805,7 +58847,7 @@
     </row>
     <row r="3547" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3547" s="1" t="s">
-        <v>6121</v>
+        <v>6120</v>
       </c>
       <c r="B3547" s="2">
         <v>1.395985571</v>
@@ -58816,7 +58858,7 @@
     </row>
     <row r="3548" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3548" s="1" t="s">
-        <v>6122</v>
+        <v>6121</v>
       </c>
       <c r="B3548" s="2">
         <v>1.397607324</v>
@@ -58871,7 +58913,7 @@
     </row>
     <row r="3553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3553" s="1" t="s">
-        <v>6123</v>
+        <v>6122</v>
       </c>
       <c r="B3553" s="2">
         <v>1.424607913</v>
@@ -58893,7 +58935,7 @@
     </row>
     <row r="3555" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3555" s="1" t="s">
-        <v>6124</v>
+        <v>6123</v>
       </c>
       <c r="B3555" s="2">
         <v>1.4344850979999999</v>
@@ -58904,7 +58946,7 @@
     </row>
     <row r="3556" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3556" s="1" t="s">
-        <v>6125</v>
+        <v>6124</v>
       </c>
       <c r="B3556" s="2">
         <v>1.43816396</v>
@@ -59113,7 +59155,7 @@
     </row>
     <row r="3575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3575" s="1" t="s">
-        <v>6126</v>
+        <v>6125</v>
       </c>
       <c r="B3575" s="2">
         <v>1.589074637</v>
@@ -59146,7 +59188,7 @@
     </row>
     <row r="3578" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3578" s="1" t="s">
-        <v>6127</v>
+        <v>6126</v>
       </c>
       <c r="B3578" s="2">
         <v>1.591205027</v>
@@ -59201,7 +59243,7 @@
     </row>
     <row r="3583" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3583" s="1" t="s">
-        <v>6128</v>
+        <v>6127</v>
       </c>
       <c r="B3583" s="2">
         <v>1.623588061</v>
@@ -59311,7 +59353,7 @@
     </row>
     <row r="3593" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3593" s="1" t="s">
-        <v>6129</v>
+        <v>6128</v>
       </c>
       <c r="B3593" s="2">
         <v>1.668703042</v>
@@ -59366,7 +59408,7 @@
     </row>
     <row r="3598" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3598" s="1" t="s">
-        <v>6130</v>
+        <v>6129</v>
       </c>
       <c r="B3598" s="2">
         <v>1.6936483360000001</v>
@@ -59476,7 +59518,7 @@
     </row>
     <row r="3608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3608" s="1" t="s">
-        <v>6131</v>
+        <v>6130</v>
       </c>
       <c r="B3608" s="2">
         <v>1.7661765110000001</v>
@@ -59509,7 +59551,7 @@
     </row>
     <row r="3611" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3611" s="1" t="s">
-        <v>6132</v>
+        <v>6131</v>
       </c>
       <c r="B3611" s="2">
         <v>1.7967748180000001</v>
@@ -59575,7 +59617,7 @@
     </row>
     <row r="3617" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3617" s="1" t="s">
-        <v>6133</v>
+        <v>6132</v>
       </c>
       <c r="B3617" s="2">
         <v>1.831480177</v>
@@ -59630,7 +59672,7 @@
     </row>
     <row r="3622" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3622" s="1" t="s">
-        <v>6134</v>
+        <v>6133</v>
       </c>
       <c r="B3622" s="2">
         <v>1.8538284979999999</v>
@@ -59762,7 +59804,7 @@
     </row>
     <row r="3634" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3634" s="1" t="s">
-        <v>6135</v>
+        <v>6134</v>
       </c>
       <c r="B3634" s="2">
         <v>1.9008181719999999</v>
@@ -59773,7 +59815,7 @@
     </row>
     <row r="3635" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3635" s="1" t="s">
-        <v>6136</v>
+        <v>6135</v>
       </c>
       <c r="B3635" s="2">
         <v>1.9238952819999999</v>
@@ -59795,7 +59837,7 @@
     </row>
     <row r="3637" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3637" s="1" t="s">
-        <v>6137</v>
+        <v>6136</v>
       </c>
       <c r="B3637" s="2">
         <v>1.957233067</v>
@@ -59861,7 +59903,7 @@
     </row>
     <row r="3643" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3643" s="1" t="s">
-        <v>6138</v>
+        <v>6137</v>
       </c>
       <c r="B3643" s="2">
         <v>2.0318165480000001</v>
@@ -59872,7 +59914,7 @@
     </row>
     <row r="3644" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3644" s="1" t="s">
-        <v>6139</v>
+        <v>6138</v>
       </c>
       <c r="B3644" s="2">
         <v>2.0321414660000001</v>
@@ -59960,7 +60002,7 @@
     </row>
     <row r="3652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3652" s="1" t="s">
-        <v>6140</v>
+        <v>6139</v>
       </c>
       <c r="B3652" s="2">
         <v>2.0894886760000002</v>
@@ -60059,7 +60101,7 @@
     </row>
     <row r="3661" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3661" s="1" t="s">
-        <v>6141</v>
+        <v>6140</v>
       </c>
       <c r="B3661" s="2">
         <v>2.1478682349999998</v>
@@ -60191,7 +60233,7 @@
     </row>
     <row r="3673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3673" s="1" t="s">
-        <v>6142</v>
+        <v>6141</v>
       </c>
       <c r="B3673" s="2">
         <v>2.276809262</v>
@@ -60202,7 +60244,7 @@
     </row>
     <row r="3674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3674" s="1" t="s">
-        <v>6143</v>
+        <v>6142</v>
       </c>
       <c r="B3674" s="2">
         <v>2.2769205750000001</v>
@@ -60246,7 +60288,7 @@
     </row>
     <row r="3678" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3678" s="1" t="s">
-        <v>6144</v>
+        <v>6143</v>
       </c>
       <c r="B3678" s="2">
         <v>2.292721325</v>
@@ -60411,7 +60453,7 @@
     </row>
     <row r="3693" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3693" s="1" t="s">
-        <v>6145</v>
+        <v>6144</v>
       </c>
       <c r="B3693" s="2">
         <v>2.3451781619999998</v>
@@ -60433,7 +60475,7 @@
     </row>
     <row r="3695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3695" s="1" t="s">
-        <v>6146</v>
+        <v>6145</v>
       </c>
       <c r="B3695" s="2">
         <v>2.3548241330000002</v>
@@ -60488,7 +60530,7 @@
     </row>
     <row r="3700" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3700" s="1" t="s">
-        <v>6147</v>
+        <v>6146</v>
       </c>
       <c r="B3700" s="2">
         <v>2.3700007959999998</v>
@@ -60532,7 +60574,7 @@
     </row>
     <row r="3704" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3704" s="1" t="s">
-        <v>6148</v>
+        <v>6147</v>
       </c>
       <c r="B3704" s="2">
         <v>2.3835193119999998</v>
@@ -60565,7 +60607,7 @@
     </row>
     <row r="3707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3707" s="1" t="s">
-        <v>6149</v>
+        <v>6148</v>
       </c>
       <c r="B3707" s="2">
         <v>2.4056303969999999</v>
@@ -60587,7 +60629,7 @@
     </row>
     <row r="3709" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3709" s="1" t="s">
-        <v>6150</v>
+        <v>6149</v>
       </c>
       <c r="B3709" s="2">
         <v>2.411337091</v>
@@ -60697,7 +60739,7 @@
     </row>
     <row r="3719" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3719" s="1" t="s">
-        <v>6151</v>
+        <v>6150</v>
       </c>
       <c r="B3719" s="2">
         <v>2.468428361</v>
@@ -60719,7 +60761,7 @@
     </row>
     <row r="3721" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3721" s="1" t="s">
-        <v>6152</v>
+        <v>6151</v>
       </c>
       <c r="B3721" s="2">
         <v>2.4976920150000002</v>
@@ -60862,7 +60904,7 @@
     </row>
     <row r="3734" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3734" s="1" t="s">
-        <v>6153</v>
+        <v>6152</v>
       </c>
       <c r="B3734" s="2">
         <v>2.5409612080000001</v>
@@ -60884,7 +60926,7 @@
     </row>
     <row r="3736" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3736" s="1" t="s">
-        <v>6154</v>
+        <v>6153</v>
       </c>
       <c r="B3736" s="2">
         <v>2.5686897110000002</v>
@@ -60939,7 +60981,7 @@
     </row>
     <row r="3741" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3741" s="1" t="s">
-        <v>6155</v>
+        <v>6154</v>
       </c>
       <c r="B3741" s="2">
         <v>2.6129192040000002</v>
@@ -60994,7 +61036,7 @@
     </row>
     <row r="3746" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3746" s="1" t="s">
-        <v>6156</v>
+        <v>6155</v>
       </c>
       <c r="B3746" s="2">
         <v>2.6404977000000001</v>
@@ -61060,7 +61102,7 @@
     </row>
     <row r="3752" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3752" s="1" t="s">
-        <v>6157</v>
+        <v>6156</v>
       </c>
       <c r="B3752" s="2">
         <v>2.6812046660000002</v>
@@ -61269,7 +61311,7 @@
     </row>
     <row r="3771" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3771" s="1" t="s">
-        <v>6158</v>
+        <v>6157</v>
       </c>
       <c r="B3771" s="2">
         <v>2.7958367970000002</v>
@@ -61280,7 +61322,7 @@
     </row>
     <row r="3772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3772" s="1" t="s">
-        <v>6159</v>
+        <v>6158</v>
       </c>
       <c r="B3772" s="2">
         <v>2.8018807460000001</v>
@@ -61379,7 +61421,7 @@
     </row>
     <row r="3781" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3781" s="1" t="s">
-        <v>6160</v>
+        <v>6159</v>
       </c>
       <c r="B3781" s="2">
         <v>2.860483511</v>
@@ -61412,7 +61454,7 @@
     </row>
     <row r="3784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3784" s="1" t="s">
-        <v>6161</v>
+        <v>6160</v>
       </c>
       <c r="B3784" s="2">
         <v>2.9047712899999998</v>
@@ -61445,7 +61487,7 @@
     </row>
     <row r="3787" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3787" s="1" t="s">
-        <v>6162</v>
+        <v>6161</v>
       </c>
       <c r="B3787" s="2">
         <v>2.9306271700000002</v>
@@ -61456,7 +61498,7 @@
     </row>
     <row r="3788" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3788" s="1" t="s">
-        <v>6163</v>
+        <v>6162</v>
       </c>
       <c r="B3788" s="2">
         <v>2.9359044160000001</v>
@@ -61478,7 +61520,7 @@
     </row>
     <row r="3790" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3790" s="1" t="s">
-        <v>6164</v>
+        <v>6163</v>
       </c>
       <c r="B3790" s="2">
         <v>2.9980245019999998</v>
@@ -61632,7 +61674,7 @@
     </row>
     <row r="3804" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3804" s="1" t="s">
-        <v>6165</v>
+        <v>6164</v>
       </c>
       <c r="B3804" s="2">
         <v>3.1156514089999998</v>
@@ -61643,7 +61685,7 @@
     </row>
     <row r="3805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3805" s="1" t="s">
-        <v>6166</v>
+        <v>6165</v>
       </c>
       <c r="B3805" s="2">
         <v>3.1177669610000001</v>
@@ -61742,7 +61784,7 @@
     </row>
     <row r="3814" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3814" s="1" t="s">
-        <v>6167</v>
+        <v>6166</v>
       </c>
       <c r="B3814" s="2">
         <v>3.1421592459999999</v>
@@ -61819,7 +61861,7 @@
     </row>
     <row r="3821" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3821" s="1" t="s">
-        <v>6168</v>
+        <v>6167</v>
       </c>
       <c r="B3821" s="2">
         <v>3.2377869929999998</v>
@@ -61830,7 +61872,7 @@
     </row>
     <row r="3822" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3822" s="1" t="s">
-        <v>6169</v>
+        <v>6168</v>
       </c>
       <c r="B3822" s="2">
         <v>3.2515284059999998</v>
@@ -61962,7 +62004,7 @@
     </row>
     <row r="3834" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3834" s="1" t="s">
-        <v>6170</v>
+        <v>6169</v>
       </c>
       <c r="B3834" s="2">
         <v>3.3414294080000002</v>
@@ -62017,7 +62059,7 @@
     </row>
     <row r="3839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3839" s="1" t="s">
-        <v>6171</v>
+        <v>6170</v>
       </c>
       <c r="B3839" s="2">
         <v>3.3676354380000002</v>
@@ -62061,7 +62103,7 @@
     </row>
     <row r="3843" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3843" s="1" t="s">
-        <v>6172</v>
+        <v>6171</v>
       </c>
       <c r="B3843" s="2">
         <v>3.3949732319999999</v>
@@ -62501,7 +62543,7 @@
     </row>
     <row r="3883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3883" s="1" t="s">
-        <v>6173</v>
+        <v>6172</v>
       </c>
       <c r="B3883" s="2">
         <v>3.6379266260000001</v>
@@ -62512,7 +62554,7 @@
     </row>
     <row r="3884" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3884" s="1" t="s">
-        <v>6174</v>
+        <v>6173</v>
       </c>
       <c r="B3884" s="2">
         <v>3.6597689309999999</v>
@@ -62545,7 +62587,7 @@
     </row>
     <row r="3887" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3887" s="1" t="s">
-        <v>6175</v>
+        <v>6174</v>
       </c>
       <c r="B3887" s="2">
         <v>3.713057058</v>
@@ -62666,7 +62708,7 @@
     </row>
     <row r="3898" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3898" s="1" t="s">
-        <v>6176</v>
+        <v>6175</v>
       </c>
       <c r="B3898" s="2">
         <v>3.8071236060000002</v>
@@ -62831,7 +62873,7 @@
     </row>
     <row r="3913" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3913" s="1" t="s">
-        <v>6177</v>
+        <v>6176</v>
       </c>
       <c r="B3913" s="2">
         <v>3.9057998459999999</v>
@@ -62864,7 +62906,7 @@
     </row>
     <row r="3916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3916" s="1" t="s">
-        <v>6178</v>
+        <v>6177</v>
       </c>
       <c r="B3916" s="2">
         <v>3.9335110809999998</v>
@@ -62886,7 +62928,7 @@
     </row>
     <row r="3918" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3918" s="1" t="s">
-        <v>6179</v>
+        <v>6178</v>
       </c>
       <c r="B3918" s="2">
         <v>3.9349800620000002</v>
@@ -62941,7 +62983,7 @@
     </row>
     <row r="3923" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3923" s="1" t="s">
-        <v>6180</v>
+        <v>6179</v>
       </c>
       <c r="B3923" s="2">
         <v>3.9700053209999999</v>
@@ -62963,7 +63005,7 @@
     </row>
     <row r="3925" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3925" s="1" t="s">
-        <v>6181</v>
+        <v>6180</v>
       </c>
       <c r="B3925" s="2">
         <v>3.9764999219999999</v>
@@ -62996,7 +63038,7 @@
     </row>
     <row r="3928" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3928" s="1" t="s">
-        <v>6182</v>
+        <v>6181</v>
       </c>
       <c r="B3928" s="2">
         <v>4.0049128920000001</v>
@@ -63040,7 +63082,7 @@
     </row>
     <row r="3932" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3932" s="1" t="s">
-        <v>6183</v>
+        <v>6182</v>
       </c>
       <c r="B3932" s="2">
         <v>4.0175670759999997</v>
@@ -63106,7 +63148,7 @@
     </row>
     <row r="3938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3938" s="1" t="s">
-        <v>6184</v>
+        <v>6183</v>
       </c>
       <c r="B3938" s="2">
         <v>4.0484231409999998</v>
@@ -63194,7 +63236,7 @@
     </row>
     <row r="3946" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3946" s="1" t="s">
-        <v>6185</v>
+        <v>6184</v>
       </c>
       <c r="B3946" s="2">
         <v>4.1066648209999999</v>
@@ -63205,7 +63247,7 @@
     </row>
     <row r="3947" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3947" s="1" t="s">
-        <v>6186</v>
+        <v>6185</v>
       </c>
       <c r="B3947" s="2">
         <v>4.1073262450000003</v>
@@ -63216,7 +63258,7 @@
     </row>
     <row r="3948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3948" s="1" t="s">
-        <v>6187</v>
+        <v>6186</v>
       </c>
       <c r="B3948" s="2">
         <v>4.1084984000000002</v>
@@ -63293,7 +63335,7 @@
     </row>
     <row r="3955" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3955" s="1" t="s">
-        <v>6188</v>
+        <v>6187</v>
       </c>
       <c r="B3955" s="2">
         <v>4.1790860629999997</v>
@@ -63425,7 +63467,7 @@
     </row>
     <row r="3967" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3967" s="1" t="s">
-        <v>6189</v>
+        <v>6188</v>
       </c>
       <c r="B3967" s="2">
         <v>4.2974466939999996</v>
@@ -63513,7 +63555,7 @@
     </row>
     <row r="3975" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3975" s="1" t="s">
-        <v>6190</v>
+        <v>6189</v>
       </c>
       <c r="B3975" s="2">
         <v>4.3836508260000002</v>
@@ -63689,7 +63731,7 @@
     </row>
     <row r="3991" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3991" s="1" t="s">
-        <v>6191</v>
+        <v>6190</v>
       </c>
       <c r="B3991" s="2">
         <v>4.52691087</v>
@@ -63744,7 +63786,7 @@
     </row>
     <row r="3996" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3996" s="1" t="s">
-        <v>6192</v>
+        <v>6191</v>
       </c>
       <c r="B3996" s="2">
         <v>4.5629699019999999</v>
@@ -63777,7 +63819,7 @@
     </row>
     <row r="3999" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3999" s="1" t="s">
-        <v>6193</v>
+        <v>6192</v>
       </c>
       <c r="B3999" s="2">
         <v>4.5802185409999998</v>
@@ -63788,7 +63830,7 @@
     </row>
     <row r="4000" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4000" s="1" t="s">
-        <v>6194</v>
+        <v>6193</v>
       </c>
       <c r="B4000" s="2">
         <v>4.6001855630000001</v>
@@ -63854,7 +63896,7 @@
     </row>
     <row r="4006" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4006" s="1" t="s">
-        <v>6195</v>
+        <v>6194</v>
       </c>
       <c r="B4006" s="2">
         <v>4.6460586240000001</v>
@@ -63865,7 +63907,7 @@
     </row>
     <row r="4007" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4007" s="1" t="s">
-        <v>6196</v>
+        <v>6195</v>
       </c>
       <c r="B4007" s="2">
         <v>4.6623646320000001</v>
@@ -63876,7 +63918,7 @@
     </row>
     <row r="4008" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4008" s="1" t="s">
-        <v>6197</v>
+        <v>6196</v>
       </c>
       <c r="B4008" s="2">
         <v>4.6629526569999999</v>
@@ -63909,7 +63951,7 @@
     </row>
     <row r="4011" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4011" s="1" t="s">
-        <v>6198</v>
+        <v>6197</v>
       </c>
       <c r="B4011" s="2">
         <v>4.6685776470000002</v>
@@ -63964,7 +64006,7 @@
     </row>
     <row r="4016" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4016" s="1" t="s">
-        <v>6199</v>
+        <v>6198</v>
       </c>
       <c r="B4016" s="2">
         <v>4.6837031920000003</v>
@@ -64030,7 +64072,7 @@
     </row>
     <row r="4022" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4022" s="1" t="s">
-        <v>6200</v>
+        <v>6199</v>
       </c>
       <c r="B4022" s="2">
         <v>4.7156287990000001</v>
@@ -64162,7 +64204,7 @@
     </row>
     <row r="4034" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4034" s="1" t="s">
-        <v>6201</v>
+        <v>6200</v>
       </c>
       <c r="B4034" s="2">
         <v>4.8150668510000001</v>
@@ -64305,7 +64347,7 @@
     </row>
     <row r="4047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4047" s="1" t="s">
-        <v>6202</v>
+        <v>6201</v>
       </c>
       <c r="B4047" s="2">
         <v>4.8757772170000004</v>
@@ -64316,7 +64358,7 @@
     </row>
     <row r="4048" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4048" s="1" t="s">
-        <v>6203</v>
+        <v>6202</v>
       </c>
       <c r="B4048" s="2">
         <v>4.8778686630000001</v>
@@ -64327,7 +64369,7 @@
     </row>
     <row r="4049" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4049" s="1" t="s">
-        <v>6204</v>
+        <v>6203</v>
       </c>
       <c r="B4049" s="2">
         <v>4.8911978420000004</v>
@@ -64448,7 +64490,7 @@
     </row>
     <row r="4060" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4060" s="1" t="s">
-        <v>6205</v>
+        <v>6204</v>
       </c>
       <c r="B4060" s="2">
         <v>4.9784638990000003</v>
@@ -64503,7 +64545,7 @@
     </row>
     <row r="4065" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4065" s="1" t="s">
-        <v>6206</v>
+        <v>6205</v>
       </c>
       <c r="B4065" s="2">
         <v>5.0285044040000004</v>
@@ -64514,7 +64556,7 @@
     </row>
     <row r="4066" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4066" s="1" t="s">
-        <v>6207</v>
+        <v>6206</v>
       </c>
       <c r="B4066" s="2">
         <v>5.0291577299999997</v>
@@ -64569,7 +64611,7 @@
     </row>
     <row r="4071" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4071" s="1" t="s">
-        <v>6208</v>
+        <v>6207</v>
       </c>
       <c r="B4071" s="2">
         <v>5.0690677820000003</v>
@@ -64624,7 +64666,7 @@
     </row>
     <row r="4076" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4076" s="1" t="s">
-        <v>6209</v>
+        <v>6208</v>
       </c>
       <c r="B4076" s="2">
         <v>5.1145271770000003</v>
@@ -64712,7 +64754,7 @@
     </row>
     <row r="4084" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4084" s="1" t="s">
-        <v>6210</v>
+        <v>6209</v>
       </c>
       <c r="B4084" s="2">
         <v>5.1581075299999997</v>
@@ -64811,7 +64853,7 @@
     </row>
     <row r="4093" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4093" s="1" t="s">
-        <v>6211</v>
+        <v>6210</v>
       </c>
       <c r="B4093" s="2">
         <v>5.2127013800000004</v>
@@ -64844,7 +64886,7 @@
     </row>
     <row r="4096" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4096" s="1" t="s">
-        <v>6212</v>
+        <v>6211</v>
       </c>
       <c r="B4096" s="2">
         <v>5.2293078629999998</v>
@@ -64921,7 +64963,7 @@
     </row>
     <row r="4103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4103" s="1" t="s">
-        <v>6213</v>
+        <v>6212</v>
       </c>
       <c r="B4103" s="2">
         <v>5.3006279010000004</v>
@@ -64976,7 +65018,7 @@
     </row>
     <row r="4108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4108" s="1" t="s">
-        <v>6214</v>
+        <v>6213</v>
       </c>
       <c r="B4108" s="2">
         <v>5.3628342489999996</v>
@@ -64987,7 +65029,7 @@
     </row>
     <row r="4109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4109" s="1" t="s">
-        <v>6215</v>
+        <v>6214</v>
       </c>
       <c r="B4109" s="2">
         <v>5.3872025150000002</v>
@@ -65020,7 +65062,7 @@
     </row>
     <row r="4112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4112" s="1" t="s">
-        <v>6216</v>
+        <v>6215</v>
       </c>
       <c r="B4112" s="2">
         <v>5.3908641929999996</v>
@@ -65075,7 +65117,7 @@
     </row>
     <row r="4117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4117" s="1" t="s">
-        <v>6217</v>
+        <v>6216</v>
       </c>
       <c r="B4117" s="2">
         <v>5.4027872280000002</v>
@@ -65086,7 +65128,7 @@
     </row>
     <row r="4118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4118" s="1" t="s">
-        <v>6218</v>
+        <v>6217</v>
       </c>
       <c r="B4118" s="2">
         <v>5.4053296949999998</v>
@@ -65229,7 +65271,7 @@
     </row>
     <row r="4131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4131" s="1" t="s">
-        <v>6219</v>
+        <v>6218</v>
       </c>
       <c r="B4131" s="2">
         <v>5.457952047</v>
@@ -65240,7 +65282,7 @@
     </row>
     <row r="4132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4132" s="1" t="s">
-        <v>6220</v>
+        <v>6219</v>
       </c>
       <c r="B4132" s="2">
         <v>5.5140690040000004</v>
@@ -65284,7 +65326,7 @@
     </row>
     <row r="4136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4136" s="1" t="s">
-        <v>6221</v>
+        <v>6220</v>
       </c>
       <c r="B4136" s="2">
         <v>5.5435970450000003</v>
@@ -65383,7 +65425,7 @@
     </row>
     <row r="4145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4145" s="1" t="s">
-        <v>6222</v>
+        <v>6221</v>
       </c>
       <c r="B4145" s="2">
         <v>5.630672949</v>
@@ -65416,7 +65458,7 @@
     </row>
     <row r="4148" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4148" s="1" t="s">
-        <v>6223</v>
+        <v>6222</v>
       </c>
       <c r="B4148" s="2">
         <v>5.6503440940000003</v>
@@ -65438,7 +65480,7 @@
     </row>
     <row r="4150" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4150" s="1" t="s">
-        <v>6224</v>
+        <v>6223</v>
       </c>
       <c r="B4150" s="2">
         <v>5.6604916479999998</v>
@@ -65449,7 +65491,7 @@
     </row>
     <row r="4151" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4151" s="1" t="s">
-        <v>6225</v>
+        <v>6224</v>
       </c>
       <c r="B4151" s="2">
         <v>5.6789230379999998</v>
@@ -65460,7 +65502,7 @@
     </row>
     <row r="4152" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4152" s="1" t="s">
-        <v>6226</v>
+        <v>6225</v>
       </c>
       <c r="B4152" s="2">
         <v>5.6794494640000002</v>
@@ -65471,7 +65513,7 @@
     </row>
     <row r="4153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4153" s="1" t="s">
-        <v>6227</v>
+        <v>6226</v>
       </c>
       <c r="B4153" s="2">
         <v>5.7027923710000001</v>
@@ -65515,7 +65557,7 @@
     </row>
     <row r="4157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4157" s="1" t="s">
-        <v>6228</v>
+        <v>6227</v>
       </c>
       <c r="B4157" s="2">
         <v>5.7365761319999997</v>
@@ -65548,7 +65590,7 @@
     </row>
     <row r="4160" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4160" s="1" t="s">
-        <v>6229</v>
+        <v>6228</v>
       </c>
       <c r="B4160" s="2">
         <v>5.7501604510000002</v>
@@ -65603,7 +65645,7 @@
     </row>
     <row r="4165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4165" s="1" t="s">
-        <v>6230</v>
+        <v>6229</v>
       </c>
       <c r="B4165" s="2">
         <v>5.7832897399999998</v>
@@ -65768,7 +65810,7 @@
     </row>
     <row r="4180" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4180" s="1" t="s">
-        <v>6231</v>
+        <v>6230</v>
       </c>
       <c r="B4180" s="2">
         <v>5.8695571119999999</v>
@@ -65779,7 +65821,7 @@
     </row>
     <row r="4181" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4181" s="1" t="s">
-        <v>6232</v>
+        <v>6231</v>
       </c>
       <c r="B4181" s="2">
         <v>5.8802010830000002</v>
@@ -65790,7 +65832,7 @@
     </row>
     <row r="4182" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4182" s="1" t="s">
-        <v>6233</v>
+        <v>6232</v>
       </c>
       <c r="B4182" s="2">
         <v>5.8941914779999998</v>
@@ -65889,7 +65931,7 @@
     </row>
     <row r="4191" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4191" s="1" t="s">
-        <v>6234</v>
+        <v>6233</v>
       </c>
       <c r="B4191" s="2">
         <v>6.0024837619999998</v>
@@ -65966,7 +66008,7 @@
     </row>
     <row r="4198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4198" s="1" t="s">
-        <v>6235</v>
+        <v>6234</v>
       </c>
       <c r="B4198" s="2">
         <v>6.0672333710000004</v>
@@ -66109,7 +66151,7 @@
     </row>
     <row r="4211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4211" s="1" t="s">
-        <v>6236</v>
+        <v>6235</v>
       </c>
       <c r="B4211" s="2">
         <v>6.1477933580000004</v>
@@ -66175,7 +66217,7 @@
     </row>
     <row r="4217" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4217" s="1" t="s">
-        <v>6237</v>
+        <v>6236</v>
       </c>
       <c r="B4217" s="2">
         <v>6.1921445329999996</v>
@@ -66219,7 +66261,7 @@
     </row>
     <row r="4221" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4221" s="1" t="s">
-        <v>6238</v>
+        <v>6237</v>
       </c>
       <c r="B4221" s="2">
         <v>6.22813105</v>
@@ -66241,7 +66283,7 @@
     </row>
     <row r="4223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4223" s="1" t="s">
-        <v>6239</v>
+        <v>6238</v>
       </c>
       <c r="B4223" s="2">
         <v>6.2601963459999999</v>
@@ -66307,7 +66349,7 @@
     </row>
     <row r="4229" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4229" s="1" t="s">
-        <v>6240</v>
+        <v>6239</v>
       </c>
       <c r="B4229" s="2">
         <v>6.3137439210000004</v>
@@ -66362,7 +66404,7 @@
     </row>
     <row r="4234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4234" s="1" t="s">
-        <v>6241</v>
+        <v>6240</v>
       </c>
       <c r="B4234" s="2">
         <v>6.3376613879999999</v>
@@ -66384,7 +66426,7 @@
     </row>
     <row r="4236" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4236" s="1" t="s">
-        <v>6242</v>
+        <v>6241</v>
       </c>
       <c r="B4236" s="2">
         <v>6.3433373819999996</v>
@@ -66406,7 +66448,7 @@
     </row>
     <row r="4238" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4238" s="1" t="s">
-        <v>6243</v>
+        <v>6242</v>
       </c>
       <c r="B4238" s="2">
         <v>6.3561308519999997</v>
@@ -66439,7 +66481,7 @@
     </row>
     <row r="4241" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4241" s="1" t="s">
-        <v>6244</v>
+        <v>6243</v>
       </c>
       <c r="B4241" s="2">
         <v>6.3778187190000004</v>
@@ -66483,7 +66525,7 @@
     </row>
     <row r="4245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4245" s="1" t="s">
-        <v>6245</v>
+        <v>6244</v>
       </c>
       <c r="B4245" s="2">
         <v>6.3957496120000004</v>
@@ -66560,7 +66602,7 @@
     </row>
     <row r="4252" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4252" s="1" t="s">
-        <v>6246</v>
+        <v>6245</v>
       </c>
       <c r="B4252" s="2">
         <v>6.4602879660000001</v>
@@ -66626,7 +66668,7 @@
     </row>
     <row r="4258" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4258" s="1" t="s">
-        <v>6247</v>
+        <v>6246</v>
       </c>
       <c r="B4258" s="2">
         <v>6.481863186</v>
@@ -66648,7 +66690,7 @@
     </row>
     <row r="4260" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4260" s="1" t="s">
-        <v>6248</v>
+        <v>6247</v>
       </c>
       <c r="B4260" s="2">
         <v>6.4934096200000004</v>
@@ -66736,7 +66778,7 @@
     </row>
     <row r="4268" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4268" s="1" t="s">
-        <v>6249</v>
+        <v>6248</v>
       </c>
       <c r="B4268" s="2">
         <v>6.5520083969999998</v>
@@ -66769,7 +66811,7 @@
     </row>
     <row r="4271" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4271" s="1" t="s">
-        <v>6250</v>
+        <v>6249</v>
       </c>
       <c r="B4271" s="2">
         <v>6.5837223969999998</v>
@@ -66813,7 +66855,7 @@
     </row>
     <row r="4275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4275" s="1" t="s">
-        <v>6251</v>
+        <v>6250</v>
       </c>
       <c r="B4275" s="2">
         <v>6.6262297139999999</v>
@@ -66835,7 +66877,7 @@
     </row>
     <row r="4277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4277" s="1" t="s">
-        <v>6252</v>
+        <v>6251</v>
       </c>
       <c r="B4277" s="2">
         <v>6.6810112249999998</v>
@@ -66846,7 +66888,7 @@
     </row>
     <row r="4278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4278" s="1" t="s">
-        <v>6253</v>
+        <v>6252</v>
       </c>
       <c r="B4278" s="2">
         <v>6.6873469910000001</v>
@@ -66890,7 +66932,7 @@
     </row>
     <row r="4282" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4282" s="1" t="s">
-        <v>6254</v>
+        <v>6253</v>
       </c>
       <c r="B4282" s="2">
         <v>6.697967727</v>
@@ -66923,7 +66965,7 @@
     </row>
     <row r="4285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4285" s="1" t="s">
-        <v>6255</v>
+        <v>6254</v>
       </c>
       <c r="B4285" s="2">
         <v>6.7290640599999998</v>
@@ -67011,7 +67053,7 @@
     </row>
     <row r="4293" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4293" s="1" t="s">
-        <v>6256</v>
+        <v>6255</v>
       </c>
       <c r="B4293" s="2">
         <v>6.7986485779999999</v>
@@ -67055,7 +67097,7 @@
     </row>
     <row r="4297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4297" s="1" t="s">
-        <v>6257</v>
+        <v>6256</v>
       </c>
       <c r="B4297" s="2">
         <v>6.8542320480000001</v>
@@ -67066,7 +67108,7 @@
     </row>
     <row r="4298" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4298" s="1" t="s">
-        <v>6258</v>
+        <v>6257</v>
       </c>
       <c r="B4298" s="2">
         <v>6.8543186140000003</v>
@@ -67088,7 +67130,7 @@
     </row>
     <row r="4300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4300" s="1" t="s">
-        <v>6259</v>
+        <v>6258</v>
       </c>
       <c r="B4300" s="2">
         <v>6.8624503959999998</v>
@@ -67110,7 +67152,7 @@
     </row>
     <row r="4302" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4302" s="1" t="s">
-        <v>6260</v>
+        <v>6259</v>
       </c>
       <c r="B4302" s="2">
         <v>6.8707762839999997</v>
@@ -67132,7 +67174,7 @@
     </row>
     <row r="4304" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4304" s="1" t="s">
-        <v>6261</v>
+        <v>6260</v>
       </c>
       <c r="B4304" s="2">
         <v>6.877142149</v>
@@ -67198,7 +67240,7 @@
     </row>
     <row r="4310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4310" s="1" t="s">
-        <v>6262</v>
+        <v>6261</v>
       </c>
       <c r="B4310" s="2">
         <v>6.9255247930000001</v>
@@ -67231,7 +67273,7 @@
     </row>
     <row r="4313" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4313" s="1" t="s">
-        <v>6263</v>
+        <v>6262</v>
       </c>
       <c r="B4313" s="2">
         <v>6.934022959</v>
@@ -67253,7 +67295,7 @@
     </row>
     <row r="4315" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4315" s="1" t="s">
-        <v>6264</v>
+        <v>6263</v>
       </c>
       <c r="B4315" s="2">
         <v>6.9512885019999997</v>
@@ -67440,7 +67482,7 @@
     </row>
     <row r="4332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4332" s="1" t="s">
-        <v>6265</v>
+        <v>6264</v>
       </c>
       <c r="B4332" s="2">
         <v>7.1148075049999999</v>
@@ -67451,7 +67493,7 @@
     </row>
     <row r="4333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4333" s="1" t="s">
-        <v>6266</v>
+        <v>6265</v>
       </c>
       <c r="B4333" s="2">
         <v>7.1169917570000001</v>
@@ -67605,7 +67647,7 @@
     </row>
     <row r="4347" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4347" s="1" t="s">
-        <v>6267</v>
+        <v>6266</v>
       </c>
       <c r="B4347" s="2">
         <v>7.2548097489999996</v>
@@ -67682,7 +67724,7 @@
     </row>
     <row r="4354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4354" s="1" t="s">
-        <v>6268</v>
+        <v>6267</v>
       </c>
       <c r="B4354" s="2">
         <v>7.3599993440000002</v>
@@ -67715,7 +67757,7 @@
     </row>
     <row r="4357" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4357" s="1" t="s">
-        <v>6269</v>
+        <v>6268</v>
       </c>
       <c r="B4357" s="2">
         <v>7.3892715930000001</v>
@@ -67726,7 +67768,7 @@
     </row>
     <row r="4358" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4358" s="1" t="s">
-        <v>6270</v>
+        <v>6269</v>
       </c>
       <c r="B4358" s="2">
         <v>7.3925019320000001</v>
@@ -67737,7 +67779,7 @@
     </row>
     <row r="4359" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4359" s="1" t="s">
-        <v>6271</v>
+        <v>6270</v>
       </c>
       <c r="B4359" s="2">
         <v>7.3968334240000004</v>
@@ -67770,7 +67812,7 @@
     </row>
     <row r="4362" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4362" s="1" t="s">
-        <v>6272</v>
+        <v>6271</v>
       </c>
       <c r="B4362" s="2">
         <v>7.4350537699999997</v>
@@ -67803,7 +67845,7 @@
     </row>
     <row r="4365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4365" s="1" t="s">
-        <v>6273</v>
+        <v>6272</v>
       </c>
       <c r="B4365" s="2">
         <v>7.4544352250000001</v>
@@ -67902,7 +67944,7 @@
     </row>
     <row r="4374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4374" s="1" t="s">
-        <v>6274</v>
+        <v>6273</v>
       </c>
       <c r="B4374" s="2">
         <v>7.5265137900000001</v>
@@ -67968,7 +68010,7 @@
     </row>
     <row r="4380" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4380" s="1" t="s">
-        <v>6275</v>
+        <v>6274</v>
       </c>
       <c r="B4380" s="2">
         <v>7.5688560550000004</v>
@@ -67979,7 +68021,7 @@
     </row>
     <row r="4381" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4381" s="1" t="s">
-        <v>6276</v>
+        <v>6275</v>
       </c>
       <c r="B4381" s="2">
         <v>7.5738339549999996</v>
@@ -67990,7 +68032,7 @@
     </row>
     <row r="4382" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4382" s="1" t="s">
-        <v>6277</v>
+        <v>6276</v>
       </c>
       <c r="B4382" s="2">
         <v>7.5803944740000002</v>
@@ -68001,7 +68043,7 @@
     </row>
     <row r="4383" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4383" s="1" t="s">
-        <v>6278</v>
+        <v>6277</v>
       </c>
       <c r="B4383" s="2">
         <v>7.5806595149999998</v>
@@ -68012,7 +68054,7 @@
     </row>
     <row r="4384" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4384" s="1" t="s">
-        <v>6279</v>
+        <v>6278</v>
       </c>
       <c r="B4384" s="2">
         <v>7.5819920200000004</v>
@@ -68067,7 +68109,7 @@
     </row>
     <row r="4389" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4389" s="1" t="s">
-        <v>6280</v>
+        <v>6279</v>
       </c>
       <c r="B4389" s="2">
         <v>7.638890011</v>
@@ -68243,7 +68285,7 @@
     </row>
     <row r="4405" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4405" s="1" t="s">
-        <v>6281</v>
+        <v>6280</v>
       </c>
       <c r="B4405" s="2">
         <v>7.7475935209999998</v>
@@ -68276,7 +68318,7 @@
     </row>
     <row r="4408" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4408" s="1" t="s">
-        <v>6282</v>
+        <v>6281</v>
       </c>
       <c r="B4408" s="2">
         <v>7.767300348</v>
@@ -68309,7 +68351,7 @@
     </row>
     <row r="4411" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4411" s="1" t="s">
-        <v>6283</v>
+        <v>6282</v>
       </c>
       <c r="B4411" s="2">
         <v>7.7841890060000001</v>
@@ -68375,7 +68417,7 @@
     </row>
     <row r="4417" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4417" s="1" t="s">
-        <v>6284</v>
+        <v>6283</v>
       </c>
       <c r="B4417" s="2">
         <v>7.8124689189999996</v>
@@ -68419,7 +68461,7 @@
     </row>
     <row r="4421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4421" s="1" t="s">
-        <v>6285</v>
+        <v>6284</v>
       </c>
       <c r="B4421" s="2">
         <v>7.841176945</v>
@@ -68529,7 +68571,7 @@
     </row>
     <row r="4431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4431" s="1" t="s">
-        <v>6286</v>
+        <v>6285</v>
       </c>
       <c r="B4431" s="2">
         <v>7.9649465480000003</v>
@@ -68540,7 +68582,7 @@
     </row>
     <row r="4432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4432" s="1" t="s">
-        <v>6287</v>
+        <v>6286</v>
       </c>
       <c r="B4432" s="2">
         <v>7.9653487429999998</v>
@@ -68716,7 +68758,7 @@
     </row>
     <row r="4448" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4448" s="1" t="s">
-        <v>6288</v>
+        <v>6287</v>
       </c>
       <c r="B4448" s="2">
         <v>8.1012199129999996</v>
@@ -68738,7 +68780,7 @@
     </row>
     <row r="4450" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4450" s="1" t="s">
-        <v>6289</v>
+        <v>6288</v>
       </c>
       <c r="B4450" s="2">
         <v>8.1108711220000007</v>
@@ -68782,7 +68824,7 @@
     </row>
     <row r="4454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4454" s="1" t="s">
-        <v>6290</v>
+        <v>6289</v>
       </c>
       <c r="B4454" s="2">
         <v>8.1745512569999992</v>
@@ -68837,7 +68879,7 @@
     </row>
     <row r="4459" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4459" s="1" t="s">
-        <v>6291</v>
+        <v>6290</v>
       </c>
       <c r="B4459" s="2">
         <v>8.2251529209999994</v>
@@ -69002,7 +69044,7 @@
     </row>
     <row r="4474" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4474" s="1" t="s">
-        <v>6292</v>
+        <v>6291</v>
       </c>
       <c r="B4474" s="2">
         <v>8.386523961</v>
@@ -69035,7 +69077,7 @@
     </row>
     <row r="4477" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4477" s="1" t="s">
-        <v>6293</v>
+        <v>6292</v>
       </c>
       <c r="B4477" s="2">
         <v>8.4027493639999999</v>
@@ -69057,7 +69099,7 @@
     </row>
     <row r="4479" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4479" s="1" t="s">
-        <v>6294</v>
+        <v>6293</v>
       </c>
       <c r="B4479" s="2">
         <v>8.4222314849999993</v>
@@ -69134,7 +69176,7 @@
     </row>
     <row r="4486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4486" s="1" t="s">
-        <v>6295</v>
+        <v>6294</v>
       </c>
       <c r="B4486" s="2">
         <v>8.4903342199999994</v>
@@ -69233,7 +69275,7 @@
     </row>
     <row r="4495" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4495" s="1" t="s">
-        <v>6296</v>
+        <v>6295</v>
       </c>
       <c r="B4495" s="2">
         <v>8.6291047289999998</v>
@@ -69310,7 +69352,7 @@
     </row>
     <row r="4502" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4502" s="1" t="s">
-        <v>6297</v>
+        <v>6296</v>
       </c>
       <c r="B4502" s="2">
         <v>8.7003309219999991</v>
@@ -69387,7 +69429,7 @@
     </row>
     <row r="4509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4509" s="1" t="s">
-        <v>6298</v>
+        <v>6297</v>
       </c>
       <c r="B4509" s="2">
         <v>8.7638404859999994</v>
@@ -69431,7 +69473,7 @@
     </row>
     <row r="4513" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4513" s="1" t="s">
-        <v>6299</v>
+        <v>6298</v>
       </c>
       <c r="B4513" s="2">
         <v>8.8549951129999993</v>
@@ -69596,7 +69638,7 @@
     </row>
     <row r="4528" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4528" s="1" t="s">
-        <v>6300</v>
+        <v>6299</v>
       </c>
       <c r="B4528" s="2">
         <v>8.9992607440000008</v>
@@ -69684,7 +69726,7 @@
     </row>
     <row r="4536" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4536" s="1" t="s">
-        <v>6301</v>
+        <v>6300</v>
       </c>
       <c r="B4536" s="2">
         <v>9.1259428029999992</v>
@@ -69750,7 +69792,7 @@
     </row>
     <row r="4542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4542" s="1" t="s">
-        <v>6302</v>
+        <v>6301</v>
       </c>
       <c r="B4542" s="2">
         <v>9.1688968390000003</v>
@@ -69937,7 +69979,7 @@
     </row>
     <row r="4559" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4559" s="1" t="s">
-        <v>6303</v>
+        <v>6302</v>
       </c>
       <c r="B4559" s="2">
         <v>9.2689040120000001</v>
@@ -69970,7 +70012,7 @@
     </row>
     <row r="4562" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4562" s="1" t="s">
-        <v>6304</v>
+        <v>6303</v>
       </c>
       <c r="B4562" s="2">
         <v>9.2978048710000003</v>
@@ -70025,7 +70067,7 @@
     </row>
     <row r="4567" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4567" s="1" t="s">
-        <v>6305</v>
+        <v>6304</v>
       </c>
       <c r="B4567" s="2">
         <v>9.3356327950000004</v>
@@ -70157,7 +70199,7 @@
     </row>
     <row r="4579" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4579" s="1" t="s">
-        <v>6306</v>
+        <v>6305</v>
       </c>
       <c r="B4579" s="2">
         <v>9.4930629129999993</v>
@@ -70190,7 +70232,7 @@
     </row>
     <row r="4582" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4582" s="1" t="s">
-        <v>6307</v>
+        <v>6306</v>
       </c>
       <c r="B4582" s="2">
         <v>9.5245328659999995</v>
@@ -70201,7 +70243,7 @@
     </row>
     <row r="4583" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4583" s="1" t="s">
-        <v>6308</v>
+        <v>6307</v>
       </c>
       <c r="B4583" s="2">
         <v>9.5264179739999992</v>
@@ -70212,7 +70254,7 @@
     </row>
     <row r="4584" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4584" s="1" t="s">
-        <v>6309</v>
+        <v>6308</v>
       </c>
       <c r="B4584" s="2">
         <v>9.5271269140000001</v>
@@ -70267,7 +70309,7 @@
     </row>
     <row r="4589" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4589" s="1" t="s">
-        <v>6310</v>
+        <v>6309</v>
       </c>
       <c r="B4589" s="2">
         <v>9.5605540599999994</v>
@@ -70278,7 +70320,7 @@
     </row>
     <row r="4590" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4590" s="1" t="s">
-        <v>6311</v>
+        <v>6310</v>
       </c>
       <c r="B4590" s="2">
         <v>9.5706592419999996</v>
@@ -70300,7 +70342,7 @@
     </row>
     <row r="4592" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4592" s="1" t="s">
-        <v>6312</v>
+        <v>6311</v>
       </c>
       <c r="B4592" s="2">
         <v>9.5789405900000002</v>
@@ -70377,7 +70419,7 @@
     </row>
     <row r="4599" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4599" s="1" t="s">
-        <v>6313</v>
+        <v>6312</v>
       </c>
       <c r="B4599" s="2">
         <v>9.6703859669999996</v>
@@ -70388,7 +70430,7 @@
     </row>
     <row r="4600" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4600" s="1" t="s">
-        <v>6314</v>
+        <v>6313</v>
       </c>
       <c r="B4600" s="2">
         <v>9.6938406350000008</v>
@@ -70410,7 +70452,7 @@
     </row>
     <row r="4602" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4602" s="1" t="s">
-        <v>6315</v>
+        <v>6314</v>
       </c>
       <c r="B4602" s="2">
         <v>9.7264932850000001</v>
@@ -70432,7 +70474,7 @@
     </row>
     <row r="4604" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4604" s="1" t="s">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="B4604" s="2">
         <v>9.7339769819999997</v>
@@ -70443,7 +70485,7 @@
     </row>
     <row r="4605" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4605" s="1" t="s">
-        <v>6317</v>
+        <v>6316</v>
       </c>
       <c r="B4605" s="2">
         <v>9.7420237620000005</v>
@@ -70465,7 +70507,7 @@
     </row>
     <row r="4607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4607" s="1" t="s">
-        <v>6318</v>
+        <v>6317</v>
       </c>
       <c r="B4607" s="2">
         <v>9.7464296049999994</v>
@@ -70476,7 +70518,7 @@
     </row>
     <row r="4608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4608" s="1" t="s">
-        <v>6319</v>
+        <v>6318</v>
       </c>
       <c r="B4608" s="2">
         <v>9.7472138850000007</v>
@@ -70498,7 +70540,7 @@
     </row>
     <row r="4610" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4610" s="1" t="s">
-        <v>6320</v>
+        <v>6319</v>
       </c>
       <c r="B4610" s="2">
         <v>9.7646292880000001</v>
@@ -70553,7 +70595,7 @@
     </row>
     <row r="4615" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4615" s="1" t="s">
-        <v>6321</v>
+        <v>6320</v>
       </c>
       <c r="B4615" s="2">
         <v>9.7969591979999997</v>
@@ -70586,7 +70628,7 @@
     </row>
     <row r="4618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4618" s="1" t="s">
-        <v>6322</v>
+        <v>6321</v>
       </c>
       <c r="B4618" s="2">
         <v>9.8258794680000001</v>
@@ -70674,7 +70716,7 @@
     </row>
     <row r="4626" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4626" s="1" t="s">
-        <v>6323</v>
+        <v>6322</v>
       </c>
       <c r="B4626" s="2">
         <v>10.017047740000001</v>
@@ -70839,7 +70881,7 @@
     </row>
     <row r="4641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4641" s="1" t="s">
-        <v>6324</v>
+        <v>6323</v>
       </c>
       <c r="B4641" s="2">
         <v>10.17112068</v>
@@ -70861,7 +70903,7 @@
     </row>
     <row r="4643" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4643" s="1" t="s">
-        <v>6325</v>
+        <v>6324</v>
       </c>
       <c r="B4643" s="2">
         <v>10.18650892</v>
@@ -70905,7 +70947,7 @@
     </row>
     <row r="4647" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4647" s="1" t="s">
-        <v>6326</v>
+        <v>6325</v>
       </c>
       <c r="B4647" s="2">
         <v>10.271257589999999</v>
@@ -70949,7 +70991,7 @@
     </row>
     <row r="4651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4651" s="1" t="s">
-        <v>6327</v>
+        <v>6326</v>
       </c>
       <c r="B4651" s="2">
         <v>10.29165242</v>
@@ -71191,7 +71233,7 @@
     </row>
     <row r="4673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4673" s="1" t="s">
-        <v>6328</v>
+        <v>6327</v>
       </c>
       <c r="B4673" s="2">
         <v>10.52500481</v>
@@ -71235,7 +71277,7 @@
     </row>
     <row r="4677" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4677" s="1" t="s">
-        <v>6329</v>
+        <v>6328</v>
       </c>
       <c r="B4677" s="2">
         <v>10.57456543</v>
@@ -71312,7 +71354,7 @@
     </row>
     <row r="4684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4684" s="1" t="s">
-        <v>6330</v>
+        <v>6329</v>
       </c>
       <c r="B4684" s="2">
         <v>10.63712342</v>
@@ -71334,7 +71376,7 @@
     </row>
     <row r="4686" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4686" s="1" t="s">
-        <v>6331</v>
+        <v>6330</v>
       </c>
       <c r="B4686" s="2">
         <v>10.64014412</v>
@@ -71433,7 +71475,7 @@
     </row>
     <row r="4695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4695" s="1" t="s">
-        <v>6332</v>
+        <v>6331</v>
       </c>
       <c r="B4695" s="2">
         <v>10.85233487</v>
@@ -71466,7 +71508,7 @@
     </row>
     <row r="4698" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4698" s="1" t="s">
-        <v>6333</v>
+        <v>6332</v>
       </c>
       <c r="B4698" s="2">
         <v>10.86460256</v>
@@ -71554,7 +71596,7 @@
     </row>
     <row r="4706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4706" s="1" t="s">
-        <v>6334</v>
+        <v>6333</v>
       </c>
       <c r="B4706" s="2">
         <v>10.90355647</v>
@@ -71620,7 +71662,7 @@
     </row>
     <row r="4712" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4712" s="1" t="s">
-        <v>6335</v>
+        <v>6334</v>
       </c>
       <c r="B4712" s="2">
         <v>10.95167865</v>
@@ -71895,7 +71937,7 @@
     </row>
     <row r="4737" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4737" s="1" t="s">
-        <v>6336</v>
+        <v>6335</v>
       </c>
       <c r="B4737" s="2">
         <v>11.22227477</v>
@@ -71961,7 +72003,7 @@
     </row>
     <row r="4743" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4743" s="1" t="s">
-        <v>6337</v>
+        <v>6336</v>
       </c>
       <c r="B4743" s="2">
         <v>11.36106657</v>
@@ -72049,7 +72091,7 @@
     </row>
     <row r="4751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4751" s="1" t="s">
-        <v>6338</v>
+        <v>6337</v>
       </c>
       <c r="B4751" s="2">
         <v>11.4604138</v>
@@ -72071,7 +72113,7 @@
     </row>
     <row r="4753" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4753" s="1" t="s">
-        <v>6339</v>
+        <v>6338</v>
       </c>
       <c r="B4753" s="2">
         <v>11.483183560000001</v>
@@ -72126,7 +72168,7 @@
     </row>
     <row r="4758" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4758" s="1" t="s">
-        <v>6340</v>
+        <v>6339</v>
       </c>
       <c r="B4758" s="2">
         <v>11.538331830000001</v>
@@ -72181,7 +72223,7 @@
     </row>
     <row r="4763" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4763" s="1" t="s">
-        <v>6341</v>
+        <v>6340</v>
       </c>
       <c r="B4763" s="2">
         <v>11.64358897</v>
@@ -72203,7 +72245,7 @@
     </row>
     <row r="4765" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4765" s="1" t="s">
-        <v>6342</v>
+        <v>6341</v>
       </c>
       <c r="B4765" s="2">
         <v>11.66415932</v>
@@ -72335,7 +72377,7 @@
     </row>
     <row r="4777" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4777" s="1" t="s">
-        <v>6343</v>
+        <v>6342</v>
       </c>
       <c r="B4777" s="2">
         <v>11.774588189999999</v>
@@ -72401,7 +72443,7 @@
     </row>
     <row r="4783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4783" s="1" t="s">
-        <v>6344</v>
+        <v>6343</v>
       </c>
       <c r="B4783" s="2">
         <v>11.82061964</v>
@@ -72423,7 +72465,7 @@
     </row>
     <row r="4785" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4785" s="1" t="s">
-        <v>6345</v>
+        <v>6344</v>
       </c>
       <c r="B4785" s="2">
         <v>11.82522084</v>
@@ -72478,7 +72520,7 @@
     </row>
     <row r="4790" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4790" s="1" t="s">
-        <v>6346</v>
+        <v>6345</v>
       </c>
       <c r="B4790" s="2">
         <v>11.888585089999999</v>
@@ -72522,7 +72564,7 @@
     </row>
     <row r="4794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4794" s="1" t="s">
-        <v>6347</v>
+        <v>6346</v>
       </c>
       <c r="B4794" s="2">
         <v>11.936815510000001</v>
@@ -72687,7 +72729,7 @@
     </row>
     <row r="4809" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4809" s="1" t="s">
-        <v>6348</v>
+        <v>6347</v>
       </c>
       <c r="B4809" s="2">
         <v>12.07612965</v>
@@ -72731,7 +72773,7 @@
     </row>
     <row r="4813" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4813" s="1" t="s">
-        <v>6349</v>
+        <v>6348</v>
       </c>
       <c r="B4813" s="2">
         <v>12.10788492</v>
@@ -72852,7 +72894,7 @@
     </row>
     <row r="4824" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4824" s="1" t="s">
-        <v>6350</v>
+        <v>6349</v>
       </c>
       <c r="B4824" s="2">
         <v>12.335307</v>
@@ -72863,7 +72905,7 @@
     </row>
     <row r="4825" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4825" s="1" t="s">
-        <v>6351</v>
+        <v>6350</v>
       </c>
       <c r="B4825" s="2">
         <v>12.35643084</v>
@@ -72896,7 +72938,7 @@
     </row>
     <row r="4828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4828" s="1" t="s">
-        <v>6352</v>
+        <v>6351</v>
       </c>
       <c r="B4828" s="2">
         <v>12.371539439999999</v>
@@ -72907,7 +72949,7 @@
     </row>
     <row r="4829" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4829" s="1" t="s">
-        <v>6353</v>
+        <v>6352</v>
       </c>
       <c r="B4829" s="2">
         <v>12.37329209</v>
@@ -73050,7 +73092,7 @@
     </row>
     <row r="4842" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4842" s="1" t="s">
-        <v>6354</v>
+        <v>6353</v>
       </c>
       <c r="B4842" s="2">
         <v>12.599440270000001</v>
@@ -73226,7 +73268,7 @@
     </row>
     <row r="4858" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4858" s="1" t="s">
-        <v>6355</v>
+        <v>6354</v>
       </c>
       <c r="B4858" s="2">
         <v>12.76094821</v>
@@ -73446,7 +73488,7 @@
     </row>
     <row r="4878" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4878" s="1" t="s">
-        <v>6356</v>
+        <v>6355</v>
       </c>
       <c r="B4878" s="2">
         <v>13.02898381</v>
@@ -73688,7 +73730,7 @@
     </row>
     <row r="4900" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4900" s="1" t="s">
-        <v>6357</v>
+        <v>6356</v>
       </c>
       <c r="B4900" s="2">
         <v>13.22729168</v>
@@ -73743,7 +73785,7 @@
     </row>
     <row r="4905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4905" s="1" t="s">
-        <v>6358</v>
+        <v>6357</v>
       </c>
       <c r="B4905" s="2">
         <v>13.304107549999999</v>
@@ -73952,7 +73994,7 @@
     </row>
     <row r="4924" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4924" s="1" t="s">
-        <v>6359</v>
+        <v>6358</v>
       </c>
       <c r="B4924" s="2">
         <v>13.57929786</v>
@@ -74029,7 +74071,7 @@
     </row>
     <row r="4931" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4931" s="1" t="s">
-        <v>6360</v>
+        <v>6359</v>
       </c>
       <c r="B4931" s="2">
         <v>13.80107022</v>
@@ -74260,7 +74302,7 @@
     </row>
     <row r="4952" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4952" s="1" t="s">
-        <v>6361</v>
+        <v>6360</v>
       </c>
       <c r="B4952" s="2">
         <v>14.001108220000001</v>
@@ -74282,7 +74324,7 @@
     </row>
     <row r="4954" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4954" s="1" t="s">
-        <v>6362</v>
+        <v>6361</v>
       </c>
       <c r="B4954" s="2">
         <v>14.00588703</v>
@@ -74293,7 +74335,7 @@
     </row>
     <row r="4955" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4955" s="1" t="s">
-        <v>6363</v>
+        <v>6362</v>
       </c>
       <c r="B4955" s="2">
         <v>14.013985679999999</v>
@@ -74458,7 +74500,7 @@
     </row>
     <row r="4970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4970" s="1" t="s">
-        <v>6364</v>
+        <v>6363</v>
       </c>
       <c r="B4970" s="2">
         <v>14.18926387</v>
@@ -74535,7 +74577,7 @@
     </row>
     <row r="4977" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4977" s="1" t="s">
-        <v>6365</v>
+        <v>6364</v>
       </c>
       <c r="B4977" s="2">
         <v>14.23724569</v>
@@ -74579,7 +74621,7 @@
     </row>
     <row r="4981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4981" s="1" t="s">
-        <v>6366</v>
+        <v>6365</v>
       </c>
       <c r="B4981" s="2">
         <v>14.29869295</v>
@@ -74656,7 +74698,7 @@
     </row>
     <row r="4988" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4988" s="1" t="s">
-        <v>6367</v>
+        <v>6366</v>
       </c>
       <c r="B4988" s="2">
         <v>14.41650213</v>
@@ -74678,7 +74720,7 @@
     </row>
     <row r="4990" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4990" s="1" t="s">
-        <v>6368</v>
+        <v>6367</v>
       </c>
       <c r="B4990" s="2">
         <v>14.435654339999999</v>
@@ -74722,7 +74764,7 @@
     </row>
     <row r="4994" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4994" s="1" t="s">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="B4994" s="2">
         <v>14.458938</v>
@@ -74854,7 +74896,7 @@
     </row>
     <row r="5006" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5006" s="1" t="s">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="B5006" s="2">
         <v>14.66202944</v>
@@ -74898,7 +74940,7 @@
     </row>
     <row r="5010" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5010" s="1" t="s">
-        <v>6371</v>
+        <v>6370</v>
       </c>
       <c r="B5010" s="2">
         <v>14.723816340000001</v>
@@ -75107,7 +75149,7 @@
     </row>
     <row r="5029" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5029" s="1" t="s">
-        <v>6372</v>
+        <v>6371</v>
       </c>
       <c r="B5029" s="2">
         <v>15.010255320000001</v>
@@ -75140,7 +75182,7 @@
     </row>
     <row r="5032" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5032" s="1" t="s">
-        <v>6373</v>
+        <v>6372</v>
       </c>
       <c r="B5032" s="2">
         <v>15.02773979</v>
@@ -75195,7 +75237,7 @@
     </row>
     <row r="5037" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5037" s="1" t="s">
-        <v>6374</v>
+        <v>6373</v>
       </c>
       <c r="B5037" s="2">
         <v>15.1270197</v>
@@ -75239,7 +75281,7 @@
     </row>
     <row r="5041" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5041" s="1" t="s">
-        <v>6375</v>
+        <v>6374</v>
       </c>
       <c r="B5041" s="2">
         <v>15.16186624</v>
@@ -75360,7 +75402,7 @@
     </row>
     <row r="5052" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5052" s="1" t="s">
-        <v>6376</v>
+        <v>6375</v>
       </c>
       <c r="B5052" s="2">
         <v>15.31958607</v>
@@ -75415,7 +75457,7 @@
     </row>
     <row r="5057" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5057" s="1" t="s">
-        <v>6377</v>
+        <v>6376</v>
       </c>
       <c r="B5057" s="2">
         <v>15.40494956</v>
@@ -75492,7 +75534,7 @@
     </row>
     <row r="5064" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5064" s="1" t="s">
-        <v>6378</v>
+        <v>6377</v>
       </c>
       <c r="B5064" s="2">
         <v>15.43253414</v>
@@ -75525,7 +75567,7 @@
     </row>
     <row r="5067" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5067" s="1" t="s">
-        <v>6379</v>
+        <v>6378</v>
       </c>
       <c r="B5067" s="2">
         <v>15.473707940000001</v>
@@ -75657,7 +75699,7 @@
     </row>
     <row r="5079" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5079" s="1" t="s">
-        <v>6380</v>
+        <v>6379</v>
       </c>
       <c r="B5079" s="2">
         <v>15.62880986</v>
@@ -75734,7 +75776,7 @@
     </row>
     <row r="5086" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5086" s="1" t="s">
-        <v>6381</v>
+        <v>6380</v>
       </c>
       <c r="B5086" s="2">
         <v>15.67629058</v>
@@ -75756,7 +75798,7 @@
     </row>
     <row r="5088" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5088" s="1" t="s">
-        <v>6382</v>
+        <v>6381</v>
       </c>
       <c r="B5088" s="2">
         <v>15.724562929999999</v>
@@ -75954,7 +75996,7 @@
     </row>
     <row r="5106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5106" s="1" t="s">
-        <v>6383</v>
+        <v>6382</v>
       </c>
       <c r="B5106" s="2">
         <v>15.98384282</v>
@@ -76042,7 +76084,7 @@
     </row>
     <row r="5114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5114" s="1" t="s">
-        <v>6384</v>
+        <v>6383</v>
       </c>
       <c r="B5114" s="2">
         <v>16.0901456</v>
@@ -76130,7 +76172,7 @@
     </row>
     <row r="5122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5122" s="1" t="s">
-        <v>6385</v>
+        <v>6384</v>
       </c>
       <c r="B5122" s="2">
         <v>16.140369239999998</v>
@@ -76141,7 +76183,7 @@
     </row>
     <row r="5123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5123" s="1" t="s">
-        <v>6386</v>
+        <v>6385</v>
       </c>
       <c r="B5123" s="2">
         <v>16.15664919</v>
@@ -76152,7 +76194,7 @@
     </row>
     <row r="5124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5124" s="1" t="s">
-        <v>6387</v>
+        <v>6386</v>
       </c>
       <c r="B5124" s="2">
         <v>16.167204959999999</v>
@@ -76196,7 +76238,7 @@
     </row>
     <row r="5128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5128" s="1" t="s">
-        <v>6388</v>
+        <v>6387</v>
       </c>
       <c r="B5128" s="2">
         <v>16.218176119999999</v>
@@ -76262,7 +76304,7 @@
     </row>
     <row r="5134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5134" s="1" t="s">
-        <v>6389</v>
+        <v>6388</v>
       </c>
       <c r="B5134" s="2">
         <v>16.30502693</v>
@@ -76504,7 +76546,7 @@
     </row>
     <row r="5156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5156" s="1" t="s">
-        <v>6390</v>
+        <v>6389</v>
       </c>
       <c r="B5156" s="2">
         <v>16.590543459999999</v>
@@ -76570,7 +76612,7 @@
     </row>
     <row r="5162" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5162" s="1" t="s">
-        <v>6391</v>
+        <v>6390</v>
       </c>
       <c r="B5162" s="2">
         <v>16.687910200000001</v>
@@ -76603,7 +76645,7 @@
     </row>
     <row r="5165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5165" s="1" t="s">
-        <v>6392</v>
+        <v>6391</v>
       </c>
       <c r="B5165" s="2">
         <v>16.728694489999999</v>
@@ -76724,7 +76766,7 @@
     </row>
     <row r="5176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5176" s="1" t="s">
-        <v>6393</v>
+        <v>6392</v>
       </c>
       <c r="B5176" s="2">
         <v>16.876844510000002</v>
@@ -76735,7 +76777,7 @@
     </row>
     <row r="5177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5177" s="1" t="s">
-        <v>6394</v>
+        <v>6393</v>
       </c>
       <c r="B5177" s="2">
         <v>16.88307241</v>
@@ -76878,7 +76920,7 @@
     </row>
     <row r="5190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5190" s="1" t="s">
-        <v>6395</v>
+        <v>6394</v>
       </c>
       <c r="B5190" s="2">
         <v>17.047734590000001</v>
@@ -76900,7 +76942,7 @@
     </row>
     <row r="5192" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5192" s="1" t="s">
-        <v>6396</v>
+        <v>6395</v>
       </c>
       <c r="B5192" s="2">
         <v>17.055192099999999</v>
@@ -77010,7 +77052,7 @@
     </row>
     <row r="5202" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5202" s="1" t="s">
-        <v>6397</v>
+        <v>6396</v>
       </c>
       <c r="B5202" s="2">
         <v>17.220470280000001</v>
@@ -77164,7 +77206,7 @@
     </row>
     <row r="5216" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5216" s="1" t="s">
-        <v>6398</v>
+        <v>6397</v>
       </c>
       <c r="B5216" s="2">
         <v>17.430869560000001</v>
@@ -77186,7 +77228,7 @@
     </row>
     <row r="5218" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5218" s="1" t="s">
-        <v>6399</v>
+        <v>6398</v>
       </c>
       <c r="B5218" s="2">
         <v>17.44320295</v>
@@ -77241,7 +77283,7 @@
     </row>
     <row r="5223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5223" s="1" t="s">
-        <v>6400</v>
+        <v>6399</v>
       </c>
       <c r="B5223" s="2">
         <v>17.480385479999999</v>
@@ -77274,7 +77316,7 @@
     </row>
     <row r="5226" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5226" s="1" t="s">
-        <v>6401</v>
+        <v>6400</v>
       </c>
       <c r="B5226" s="2">
         <v>17.582542750000002</v>
@@ -77318,7 +77360,7 @@
     </row>
     <row r="5230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5230" s="1" t="s">
-        <v>6402</v>
+        <v>6401</v>
       </c>
       <c r="B5230" s="2">
         <v>17.64610025</v>
@@ -77395,7 +77437,7 @@
     </row>
     <row r="5237" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5237" s="1" t="s">
-        <v>6403</v>
+        <v>6402</v>
       </c>
       <c r="B5237" s="2">
         <v>17.768519779999998</v>
@@ -77428,7 +77470,7 @@
     </row>
     <row r="5240" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5240" s="1" t="s">
-        <v>6404</v>
+        <v>6403</v>
       </c>
       <c r="B5240" s="2">
         <v>17.800405309999999</v>
@@ -77483,7 +77525,7 @@
     </row>
     <row r="5245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5245" s="1" t="s">
-        <v>6405</v>
+        <v>6404</v>
       </c>
       <c r="B5245" s="2">
         <v>17.846748210000001</v>
@@ -77604,7 +77646,7 @@
     </row>
     <row r="5256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5256" s="1" t="s">
-        <v>6406</v>
+        <v>6405</v>
       </c>
       <c r="B5256" s="2">
         <v>17.953972190000002</v>
@@ -77681,7 +77723,7 @@
     </row>
     <row r="5263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5263" s="1" t="s">
-        <v>6407</v>
+        <v>6406</v>
       </c>
       <c r="B5263" s="2">
         <v>18.073041069999999</v>
@@ -77857,7 +77899,7 @@
     </row>
     <row r="5279" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5279" s="1" t="s">
-        <v>6408</v>
+        <v>6407</v>
       </c>
       <c r="B5279" s="2">
         <v>18.250364579999999</v>
@@ -77967,7 +78009,7 @@
     </row>
     <row r="5289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5289" s="1" t="s">
-        <v>6409</v>
+        <v>6408</v>
       </c>
       <c r="B5289" s="2">
         <v>18.378500710000001</v>
@@ -78132,7 +78174,7 @@
     </row>
     <row r="5304" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5304" s="1" t="s">
-        <v>6410</v>
+        <v>6409</v>
       </c>
       <c r="B5304" s="2">
         <v>18.633676399999999</v>
@@ -78242,7 +78284,7 @@
     </row>
     <row r="5314" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5314" s="1" t="s">
-        <v>6411</v>
+        <v>6410</v>
       </c>
       <c r="B5314" s="2">
         <v>18.74561718</v>
@@ -78385,7 +78427,7 @@
     </row>
     <row r="5327" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5327" s="1" t="s">
-        <v>6412</v>
+        <v>6411</v>
       </c>
       <c r="B5327" s="2">
         <v>18.946099190000002</v>
@@ -78440,7 +78482,7 @@
     </row>
     <row r="5332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5332" s="1" t="s">
-        <v>6413</v>
+        <v>6412</v>
       </c>
       <c r="B5332" s="2">
         <v>18.98569449</v>
@@ -78473,7 +78515,7 @@
     </row>
     <row r="5335" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5335" s="1" t="s">
-        <v>6414</v>
+        <v>6413</v>
       </c>
       <c r="B5335" s="2">
         <v>18.994148679999999</v>
@@ -78583,7 +78625,7 @@
     </row>
     <row r="5345" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5345" s="1" t="s">
-        <v>6415</v>
+        <v>6414</v>
       </c>
       <c r="B5345" s="2">
         <v>19.232013510000002</v>
@@ -78704,7 +78746,7 @@
     </row>
     <row r="5356" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5356" s="1" t="s">
-        <v>6416</v>
+        <v>6415</v>
       </c>
       <c r="B5356" s="2">
         <v>19.342432809999998</v>
@@ -78737,7 +78779,7 @@
     </row>
     <row r="5359" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5359" s="1" t="s">
-        <v>6417</v>
+        <v>6416</v>
       </c>
       <c r="B5359" s="2">
         <v>19.38033854</v>
@@ -78836,7 +78878,7 @@
     </row>
     <row r="5368" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5368" s="1" t="s">
-        <v>6418</v>
+        <v>6417</v>
       </c>
       <c r="B5368" s="2">
         <v>19.567709579999999</v>
@@ -78880,7 +78922,7 @@
     </row>
     <row r="5372" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5372" s="1" t="s">
-        <v>6419</v>
+        <v>6418</v>
       </c>
       <c r="B5372" s="2">
         <v>19.653124089999999</v>
@@ -79034,7 +79076,7 @@
     </row>
     <row r="5386" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5386" s="1" t="s">
-        <v>6420</v>
+        <v>6419</v>
       </c>
       <c r="B5386" s="2">
         <v>19.82475561</v>
@@ -79111,7 +79153,7 @@
     </row>
     <row r="5393" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5393" s="1" t="s">
-        <v>6421</v>
+        <v>6420</v>
       </c>
       <c r="B5393" s="2">
         <v>19.907852890000001</v>
@@ -79397,7 +79439,7 @@
     </row>
     <row r="5419" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5419" s="1" t="s">
-        <v>6422</v>
+        <v>6421</v>
       </c>
       <c r="B5419" s="2">
         <v>20.250994819999999</v>
@@ -79562,7 +79604,7 @@
     </row>
     <row r="5434" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5434" s="1" t="s">
-        <v>6423</v>
+        <v>6422</v>
       </c>
       <c r="B5434" s="2">
         <v>20.44547545</v>
@@ -79639,7 +79681,7 @@
     </row>
     <row r="5441" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5441" s="1" t="s">
-        <v>6424</v>
+        <v>6423</v>
       </c>
       <c r="B5441" s="2">
         <v>20.52130167</v>
@@ -79716,7 +79758,7 @@
     </row>
     <row r="5448" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5448" s="1" t="s">
-        <v>6425</v>
+        <v>6424</v>
       </c>
       <c r="B5448" s="2">
         <v>20.626374210000002</v>
@@ -80332,7 +80374,7 @@
     </row>
     <row r="5504" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5504" s="1" t="s">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="B5504" s="2">
         <v>21.32465758</v>
@@ -80530,7 +80572,7 @@
     </row>
     <row r="5522" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5522" s="1" t="s">
-        <v>6427</v>
+        <v>6426</v>
       </c>
       <c r="B5522" s="2">
         <v>21.606772029999998</v>
@@ -80585,7 +80627,7 @@
     </row>
     <row r="5527" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5527" s="1" t="s">
-        <v>6428</v>
+        <v>6427</v>
       </c>
       <c r="B5527" s="2">
         <v>21.681628450000002</v>
@@ -80618,7 +80660,7 @@
     </row>
     <row r="5530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5530" s="1" t="s">
-        <v>6429</v>
+        <v>6428</v>
       </c>
       <c r="B5530" s="2">
         <v>21.71929364</v>
@@ -80706,7 +80748,7 @@
     </row>
     <row r="5538" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5538" s="1" t="s">
-        <v>6430</v>
+        <v>6429</v>
       </c>
       <c r="B5538" s="2">
         <v>21.827875599999999</v>
@@ -80882,7 +80924,7 @@
     </row>
     <row r="5554" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5554" s="1" t="s">
-        <v>6431</v>
+        <v>6430</v>
       </c>
       <c r="B5554" s="2">
         <v>22.11676168</v>
@@ -80970,7 +81012,7 @@
     </row>
     <row r="5562" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5562" s="1" t="s">
-        <v>6432</v>
+        <v>6431</v>
       </c>
       <c r="B5562" s="2">
         <v>22.255783610000002</v>
@@ -81168,7 +81210,7 @@
     </row>
     <row r="5580" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5580" s="1" t="s">
-        <v>6433</v>
+        <v>6432</v>
       </c>
       <c r="B5580" s="2">
         <v>22.65354872</v>
@@ -81498,7 +81540,7 @@
     </row>
     <row r="5610" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5610" s="1" t="s">
-        <v>6434</v>
+        <v>6433</v>
       </c>
       <c r="B5610" s="2">
         <v>23.173186680000001</v>
@@ -81674,7 +81716,7 @@
     </row>
     <row r="5626" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5626" s="1" t="s">
-        <v>6435</v>
+        <v>6434</v>
       </c>
       <c r="B5626" s="2">
         <v>23.32526571</v>
@@ -81685,7 +81727,7 @@
     </row>
     <row r="5627" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5627" s="1" t="s">
-        <v>6436</v>
+        <v>6435</v>
       </c>
       <c r="B5627" s="2">
         <v>23.35406755</v>
@@ -81982,7 +82024,7 @@
     </row>
     <row r="5654" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5654" s="1" t="s">
-        <v>6437</v>
+        <v>6436</v>
       </c>
       <c r="B5654" s="2">
         <v>23.899417549999999</v>
@@ -82092,7 +82134,7 @@
     </row>
     <row r="5664" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5664" s="1" t="s">
-        <v>6438</v>
+        <v>6437</v>
       </c>
       <c r="B5664" s="2">
         <v>24.020135440000001</v>
@@ -82367,7 +82409,7 @@
     </row>
     <row r="5689" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5689" s="1" t="s">
-        <v>6439</v>
+        <v>6438</v>
       </c>
       <c r="B5689" s="2">
         <v>24.509628729999999</v>
@@ -82477,7 +82519,7 @@
     </row>
     <row r="5699" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5699" s="1" t="s">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="B5699" s="2">
         <v>24.68520075</v>
@@ -82510,7 +82552,7 @@
     </row>
     <row r="5702" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5702" s="1" t="s">
-        <v>6441</v>
+        <v>6440</v>
       </c>
       <c r="B5702" s="2">
         <v>24.714212450000002</v>
@@ -82664,7 +82706,7 @@
     </row>
     <row r="5716" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5716" s="1" t="s">
-        <v>6442</v>
+        <v>6441</v>
       </c>
       <c r="B5716" s="2">
         <v>25.012977070000002</v>
@@ -82675,7 +82717,7 @@
     </row>
     <row r="5717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5717" s="1" t="s">
-        <v>6443</v>
+        <v>6442</v>
       </c>
       <c r="B5717" s="2">
         <v>25.022648400000001</v>
@@ -82774,7 +82816,7 @@
     </row>
     <row r="5726" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5726" s="1" t="s">
-        <v>6444</v>
+        <v>6443</v>
       </c>
       <c r="B5726" s="2">
         <v>25.238074959999999</v>
@@ -82818,7 +82860,7 @@
     </row>
     <row r="5730" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5730" s="1" t="s">
-        <v>6445</v>
+        <v>6444</v>
       </c>
       <c r="B5730" s="2">
         <v>25.272740550000002</v>
@@ -83038,7 +83080,7 @@
     </row>
     <row r="5750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5750" s="1" t="s">
-        <v>6446</v>
+        <v>6445</v>
       </c>
       <c r="B5750" s="2">
         <v>25.791132730000001</v>
@@ -83104,7 +83146,7 @@
     </row>
     <row r="5756" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5756" s="1" t="s">
-        <v>6447</v>
+        <v>6446</v>
       </c>
       <c r="B5756" s="2">
         <v>26.020123139999999</v>
@@ -83346,7 +83388,7 @@
     </row>
     <row r="5778" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5778" s="1" t="s">
-        <v>6448</v>
+        <v>6447</v>
       </c>
       <c r="B5778" s="2">
         <v>26.539328040000001</v>
@@ -83709,7 +83751,7 @@
     </row>
     <row r="5811" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5811" s="1" t="s">
-        <v>6449</v>
+        <v>6448</v>
       </c>
       <c r="B5811" s="2">
         <v>27.183563790000001</v>
@@ -83720,7 +83762,7 @@
     </row>
     <row r="5812" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5812" s="1" t="s">
-        <v>6450</v>
+        <v>6449</v>
       </c>
       <c r="B5812" s="2">
         <v>27.218379290000001</v>
@@ -84050,7 +84092,7 @@
     </row>
     <row r="5842" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5842" s="1" t="s">
-        <v>6451</v>
+        <v>6450</v>
       </c>
       <c r="B5842" s="2">
         <v>27.827978590000001</v>
@@ -84105,7 +84147,7 @@
     </row>
     <row r="5847" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5847" s="1" t="s">
-        <v>6452</v>
+        <v>6451</v>
       </c>
       <c r="B5847" s="2">
         <v>27.893662639999999</v>
@@ -84182,7 +84224,7 @@
     </row>
     <row r="5854" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5854" s="1" t="s">
-        <v>6453</v>
+        <v>6452</v>
       </c>
       <c r="B5854" s="2">
         <v>28.111662800000001</v>
@@ -84215,7 +84257,7 @@
     </row>
     <row r="5857" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5857" s="1" t="s">
-        <v>6454</v>
+        <v>6453</v>
       </c>
       <c r="B5857" s="2">
         <v>28.159892840000001</v>
@@ -84303,7 +84345,7 @@
     </row>
     <row r="5865" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5865" s="1" t="s">
-        <v>6455</v>
+        <v>6454</v>
       </c>
       <c r="B5865" s="2">
         <v>28.292355730000001</v>
@@ -84600,7 +84642,7 @@
     </row>
     <row r="5892" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5892" s="1" t="s">
-        <v>6456</v>
+        <v>6455</v>
       </c>
       <c r="B5892" s="2">
         <v>29.132157410000001</v>
@@ -84644,7 +84686,7 @@
     </row>
     <row r="5896" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5896" s="1" t="s">
-        <v>6457</v>
+        <v>6456</v>
       </c>
       <c r="B5896" s="2">
         <v>29.2269231</v>
@@ -84765,7 +84807,7 @@
     </row>
     <row r="5907" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5907" s="1" t="s">
-        <v>6458</v>
+        <v>6457</v>
       </c>
       <c r="B5907" s="2">
         <v>29.56735655</v>
@@ -84831,7 +84873,7 @@
     </row>
     <row r="5913" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5913" s="1" t="s">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="B5913" s="2">
         <v>29.745209840000001</v>
@@ -84974,7 +85016,7 @@
     </row>
     <row r="5926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5926" s="1" t="s">
-        <v>6460</v>
+        <v>6459</v>
       </c>
       <c r="B5926" s="2">
         <v>30.119590639999998</v>
@@ -85315,7 +85357,7 @@
     </row>
     <row r="5957" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5957" s="1" t="s">
-        <v>6461</v>
+        <v>6460</v>
       </c>
       <c r="B5957" s="2">
         <v>30.941450979999999</v>
@@ -87020,7 +87062,7 @@
     </row>
     <row r="6112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6112" s="1" t="s">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="B6112" s="2">
         <v>37.126015379999998</v>
@@ -90855,6 +90897,11 @@
       </c>
       <c r="C6460" s="4" t="s">
         <v>5893</v>
+      </c>
+    </row>
+    <row r="6462" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6462" s="8" t="s">
+        <v>6464</v>
       </c>
     </row>
   </sheetData>
